--- a/03_CAD/URDF/matt_robodog_rev00/reference/Coordinate_Cinematiche_matt_robodog_rev00.xlsx
+++ b/03_CAD/URDF/matt_robodog_rev00/reference/Coordinate_Cinematiche_matt_robodog_rev00.xlsx
@@ -13,7 +13,10 @@
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAD_Source_Data" sheetId="9" r:id="R3df41296733f4968"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mass_Reconciliation" sheetId="10" r:id="R00897d6d28824d0d"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physical_Property_Method" sheetId="11" r:id="Rada7cf4125ca4620"/>
+    <x:sheet xmlns:ns0="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weight_Evidence_2026-10-30" sheetId="12" ns0:id="Rnew12"/>
+    <x:sheet xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physical_Evidence_Log" sheetId="13" ns1:id="Rnew13"/>
   </x:sheets>
+  <x:calcPr fullCalcOnLoad="1"/>
 </x:workbook>
 </file>
 
@@ -1696,7 +1699,7 @@
         <x:v>Revisione</x:v>
       </x:c>
       <x:c r="D4" s="21" t="str">
-        <x:v>REV00 — Kinematics lower limit -92°</x:v>
+        <x:v>REV01-FIX — hip origin Z +2.2 mm; physical properties 2026-10-30</x:v>
       </x:c>
       <x:c r="E4" s="26" t="str">
         <x:v>Stato</x:v>
@@ -1848,8 +1851,8 @@
       <x:c r="L8" s="64" t="n">
         <x:v>47.5</x:v>
       </x:c>
-      <x:c r="M8" s="64" t="n">
-        <x:v>46.5</x:v>
+      <x:c r="M8" s="64">
+        <x:v>48.7</x:v>
       </x:c>
       <x:c r="N8" s="64" t="n">
         <x:v>-45</x:v>
@@ -1865,9 +1868,9 @@
         <x:f>IF($E8="Fixed","",$L8/1000)</x:f>
         <x:v>0.0475</x:v>
       </x:c>
-      <x:c r="R8" s="70" t="n">
+      <x:c r="R8" s="70">
         <x:f>IF($E8="Fixed","",$M8/1000)</x:f>
-        <x:v>0.0465</x:v>
+        <x:v>0.0487</x:v>
       </x:c>
       <x:c r="S8" s="269" t="n">
         <x:f>IF($E8="Fixed","",PI()/180*$N8)</x:f>
@@ -2146,8 +2149,8 @@
       <x:c r="L12" s="64" t="n">
         <x:v>-47.5</x:v>
       </x:c>
-      <x:c r="M12" s="64" t="n">
-        <x:v>46.5</x:v>
+      <x:c r="M12" s="64">
+        <x:v>48.7</x:v>
       </x:c>
       <x:c r="N12" s="64" t="n">
         <x:v>-45</x:v>
@@ -2163,9 +2166,9 @@
         <x:f>IF($E12="Fixed","",$L12/1000)</x:f>
         <x:v>-0.0475</x:v>
       </x:c>
-      <x:c r="R12" s="70" t="n">
+      <x:c r="R12" s="70">
         <x:f>IF($E12="Fixed","",$M12/1000)</x:f>
-        <x:v>0.0465</x:v>
+        <x:v>0.0487</x:v>
       </x:c>
       <x:c r="S12" s="269" t="n">
         <x:f>IF($E12="Fixed","",PI()/180*$N12)</x:f>
@@ -2444,8 +2447,8 @@
       <x:c r="L16" s="64" t="n">
         <x:v>-47.5</x:v>
       </x:c>
-      <x:c r="M16" s="64" t="n">
-        <x:v>26.5</x:v>
+      <x:c r="M16" s="64">
+        <x:v>28.7</x:v>
       </x:c>
       <x:c r="N16" s="64" t="n">
         <x:v>-45</x:v>
@@ -2461,9 +2464,9 @@
         <x:f>IF($E16="Fixed","",$L16/1000)</x:f>
         <x:v>-0.0475</x:v>
       </x:c>
-      <x:c r="R16" s="70" t="n">
+      <x:c r="R16" s="70">
         <x:f>IF($E16="Fixed","",$M16/1000)</x:f>
-        <x:v>0.0265</x:v>
+        <x:v>0.0287</x:v>
       </x:c>
       <x:c r="S16" s="269" t="n">
         <x:f>IF($E16="Fixed","",PI()/180*$N16)</x:f>
@@ -2742,8 +2745,8 @@
       <x:c r="L20" s="64" t="n">
         <x:v>47.5</x:v>
       </x:c>
-      <x:c r="M20" s="64" t="n">
-        <x:v>26.5</x:v>
+      <x:c r="M20" s="64">
+        <x:v>28.7</x:v>
       </x:c>
       <x:c r="N20" s="64" t="n">
         <x:v>-45</x:v>
@@ -2759,9 +2762,9 @@
         <x:f>IF($E20="Fixed","",$L20/1000)</x:f>
         <x:v>0.0475</x:v>
       </x:c>
-      <x:c r="R20" s="70" t="n">
+      <x:c r="R20" s="70">
         <x:f>IF($E20="Fixed","",$M20/1000)</x:f>
-        <x:v>0.0265</x:v>
+        <x:v>0.0287</x:v>
       </x:c>
       <x:c r="S20" s="269" t="n">
         <x:f>IF($E20="Fixed","",PI()/180*$N20)</x:f>
@@ -3031,7 +3034,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="289" t="str">
-        <x:v>MATDOG — Riconciliazione masse REV00</x:v>
+        <x:v>MATDOG — Riconciliazione masse REV01-FIX</x:v>
       </x:c>
       <x:c r="B1" s="289"/>
       <x:c r="C1" s="289"/>
@@ -3043,7 +3046,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="294" t="str">
-        <x:v>Il modello dinamico usa le masse CAD per-link che riconciliano esattamente i 2.480 kg dell’assieme CAD. Il peso calcolato e la misura reale sono conservati come controlli di configurazione, non come scala automatica del tensore d’inerzia.</x:v>
+        <x:v>Il modello dinamico usa le masse per-link dei report Solid Edge 2026-10-30 (1 g di risoluzione); non è stata applicata alcuna scala. Il calcolo pesi e la pesata reale (senza Jetson) sono conservati come controlli di configurazione, non come scala automatica del tensore d’inerzia.</x:v>
       </x:c>
       <x:c r="B2" s="294"/>
       <x:c r="C2" s="294"/>
@@ -3065,75 +3068,89 @@
       <x:c r="A5" s="301" t="str">
         <x:v>URDF dynamic model — CAD mass [kg]</x:v>
       </x:c>
-      <x:c r="B5" s="306" t="n">
-        <x:v>2.48</x:v>
+      <x:c r="B5" s="306">
+        <x:f>Inertial_Properties!D23</x:f>
+        <x:v>2.928</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="301" t="str">
         <x:v>CAD full assembly report [kg]</x:v>
       </x:c>
-      <x:c r="B6" s="306" t="n">
-        <x:v>2.48</x:v>
+      <x:c r="B6" s="306">
+        <x:f>CAD_Source_Data!D10</x:f>
+        <x:v>2.937</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="301" t="str">
         <x:v>Difference model vs full CAD [kg]</x:v>
       </x:c>
-      <x:c r="B7" s="306" t="n">
+      <x:c r="B7" s="306">
         <x:f>B5-B6</x:f>
-        <x:v>0</x:v>
+        <x:v>-0.008999999999999897</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="301" t="str">
-        <x:v>Weight-breakdown calculated [kg]</x:v>
-      </x:c>
-      <x:c r="B8" s="306" t="n">
-        <x:v>2.3894</x:v>
+        <x:v>Weight-breakdown calculated, WITH Jetson [kg]</x:v>
+      </x:c>
+      <x:c r="B8" s="306">
+        <x:f>('Weight_Evidence_2026-10-30'!J11+'Weight_Evidence_2026-10-30'!F16)/1000</x:f>
+        <x:v>2.9432</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="301" t="str">
-        <x:v>Physical robot measured [kg]</x:v>
-      </x:c>
-      <x:c r="B9" s="306" t="n">
-        <x:v>2.297</x:v>
+        <x:v>Physical robot measured 2026-10-30, WITHOUT Jetson [kg]</x:v>
+      </x:c>
+      <x:c r="B9" s="306">
+        <x:f>'Weight_Evidence_2026-10-30'!J2/1000</x:f>
+        <x:v>2.807</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="301" t="str">
-        <x:v>CAD model − measured robot [kg]</x:v>
-      </x:c>
-      <x:c r="B10" s="306" t="n">
-        <x:f>B5-B9</x:f>
-        <x:v>0.18299999999999983</x:v>
+        <x:v>CAD assembly without Jetson − measured robot [kg]</x:v>
+      </x:c>
+      <x:c r="B10" s="306">
+        <x:f>(B6-B12)-B9</x:f>
+        <x:v>-0.04499999999999993</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="301" t="str">
-        <x:v>CAD model − measured robot [%]</x:v>
-      </x:c>
-      <x:c r="B11" s="308" t="n">
-        <x:f>(B5-B9)/B5</x:f>
-        <x:v>0.07379032258064509</x:v>
+        <x:v>(CAD assembly without Jetson − measured robot) / CAD without Jetson</x:v>
+      </x:c>
+      <x:c r="B11" s="308">
+        <x:f>B10/(B6-B12)</x:f>
+        <x:v>-0.016292541636495267</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="301" t="str">
-        <x:v>Neck yaw actuator [kg]</x:v>
-      </x:c>
-      <x:c r="B12" s="306" t="n">
-        <x:v>0.061</x:v>
+        <x:v>Jetson Orin, inside the base_link CAD [kg]</x:v>
+      </x:c>
+      <x:c r="B12" s="306">
+        <x:f>'Weight_Evidence_2026-10-30'!F16/1000</x:f>
+        <x:v>0.175</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="310" t="str">
-        <x:v>Neck yaw actuator in REV00 17-link URDF</x:v>
+        <x:v>5th motor housing / neck yaw</x:v>
       </x:c>
       <x:c r="B13" s="310" t="str">
-        <x:v>No standalone link; not added without a dedicated mounted-frame CAD report.</x:v>
+        <x:v>Not separately modeled. The weight workbook counts 5 motor housings in the base group; whether the Solid Edge base_link mass includes the fifth is NOT stated by the evidence (UNKNOWN).</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str" s="301">
+        <x:v>Weight workbook: measured − analytic without Jetson [kg]</x:v>
+      </x:c>
+      <x:c r="B14" s="306">
+        <x:f>'Weight_Evidence_2026-10-30'!J13/1000</x:f>
+        <x:v>0.03880000000000018</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -3169,26 +3186,28 @@
       <x:c r="B17" s="301" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C17" s="306" t="n">
-        <x:v>1.282</x:v>
-      </x:c>
-      <x:c r="D17" s="306" t="n">
+      <x:c r="C17" s="306">
+        <x:f>Inertial_Properties!D5</x:f>
+        <x:v>1.828</x:v>
+      </x:c>
+      <x:c r="D17" s="306">
         <x:f>B17*C17</x:f>
-        <x:v>1.282</x:v>
-      </x:c>
-      <x:c r="E17" s="306" t="n">
-        <x:v>1.237</x:v>
-      </x:c>
-      <x:c r="F17" s="306" t="n">
+        <x:v>1.828</x:v>
+      </x:c>
+      <x:c r="E17" s="306">
+        <x:f>('Weight_Evidence_2026-10-30'!F33+'Weight_Evidence_2026-10-30'!M6+'Weight_Evidence_2026-10-30'!M7)/1000</x:f>
+        <x:v>1.8416</x:v>
+      </x:c>
+      <x:c r="F17" s="306">
         <x:f>B17*E17</x:f>
-        <x:v>1.237</x:v>
-      </x:c>
-      <x:c r="G17" s="306" t="n">
+        <x:v>1.8416</x:v>
+      </x:c>
+      <x:c r="G17" s="306">
         <x:f>D17-F17</x:f>
-        <x:v>0.04499999999999993</x:v>
+        <x:v>-0.013599999999999834</x:v>
       </x:c>
       <x:c r="H17" s="301" t="str">
-        <x:v>CAD direct</x:v>
+        <x:v>CAD direct (Solid Edge 2026-10-30)</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -3198,23 +3217,25 @@
       <x:c r="B18" s="301" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C18" s="306" t="n">
+      <x:c r="C18" s="306">
+        <x:f>Inertial_Properties!D6</x:f>
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="D18" s="306" t="n">
         <x:f>B18*C18</x:f>
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="E18" s="306" t="n">
-        <x:v>0.0506</x:v>
-      </x:c>
-      <x:c r="F18" s="306" t="n">
+      <x:c r="E18" s="306">
+        <x:f>'Weight_Evidence_2026-10-30'!F41/1000</x:f>
+        <x:v>0.0501</x:v>
+      </x:c>
+      <x:c r="F18" s="306">
         <x:f>B18*E18</x:f>
-        <x:v>0.2024</x:v>
-      </x:c>
-      <x:c r="G18" s="306" t="n">
+        <x:v>0.2004</x:v>
+      </x:c>
+      <x:c r="G18" s="306">
         <x:f>D18-F18</x:f>
-        <x:v>-0.0023999999999999855</x:v>
+        <x:v>-0.0003999999999999837</x:v>
       </x:c>
       <x:c r="H18" s="301" t="str">
         <x:v>CAD direct / link CAD report</x:v>
@@ -3227,23 +3248,25 @@
       <x:c r="B19" s="301" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C19" s="306" t="n">
-        <x:v>0.1725</x:v>
-      </x:c>
-      <x:c r="D19" s="306" t="n">
+      <x:c r="C19" s="306">
+        <x:f>Inertial_Properties!D7</x:f>
+        <x:v>0.152</x:v>
+      </x:c>
+      <x:c r="D19" s="306">
         <x:f>B19*C19</x:f>
-        <x:v>0.69</x:v>
-      </x:c>
-      <x:c r="E19" s="306" t="n">
-        <x:v>0.1597</x:v>
-      </x:c>
-      <x:c r="F19" s="306" t="n">
+        <x:v>0.608</x:v>
+      </x:c>
+      <x:c r="E19" s="306">
+        <x:f>'Weight_Evidence_2026-10-30'!F49/1000</x:f>
+        <x:v>0.152</x:v>
+      </x:c>
+      <x:c r="F19" s="306">
         <x:f>B19*E19</x:f>
-        <x:v>0.6388</x:v>
-      </x:c>
-      <x:c r="G19" s="306" t="n">
+        <x:v>0.608</x:v>
+      </x:c>
+      <x:c r="G19" s="306">
         <x:f>D19-F19</x:f>
-        <x:v>0.05119999999999991</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H19" s="301" t="str">
         <x:v>CAD direct / link CAD report</x:v>
@@ -3256,23 +3279,25 @@
       <x:c r="B20" s="301" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C20" s="306" t="n">
-        <x:v>0.0595</x:v>
-      </x:c>
-      <x:c r="D20" s="306" t="n">
+      <x:c r="C20" s="306">
+        <x:f>Inertial_Properties!D8</x:f>
+        <x:v>0.059</x:v>
+      </x:c>
+      <x:c r="D20" s="306">
         <x:f>B20*C20</x:f>
-        <x:v>0.238</x:v>
-      </x:c>
-      <x:c r="E20" s="306" t="n">
-        <x:v>0.0628</x:v>
-      </x:c>
-      <x:c r="F20" s="306" t="n">
+        <x:v>0.236</x:v>
+      </x:c>
+      <x:c r="E20" s="306">
+        <x:f>'Weight_Evidence_2026-10-30'!F57/1000</x:f>
+        <x:v>0.0593</x:v>
+      </x:c>
+      <x:c r="F20" s="306">
         <x:f>B20*E20</x:f>
-        <x:v>0.2512</x:v>
-      </x:c>
-      <x:c r="G20" s="306" t="n">
+        <x:v>0.2372</x:v>
+      </x:c>
+      <x:c r="G20" s="306">
         <x:f>D20-F20</x:f>
-        <x:v>-0.01319999999999999</x:v>
+        <x:v>-0.0012000000000000066</x:v>
       </x:c>
       <x:c r="H20" s="301" t="str">
         <x:v>CAD direct / link CAD report</x:v>
@@ -3285,23 +3310,25 @@
       <x:c r="B21" s="301" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C21" s="306" t="n">
-        <x:v>0.0175</x:v>
-      </x:c>
-      <x:c r="D21" s="306" t="n">
+      <x:c r="C21" s="306">
+        <x:f>Inertial_Properties!D9</x:f>
+        <x:v>0.014</x:v>
+      </x:c>
+      <x:c r="D21" s="306">
         <x:f>B21*C21</x:f>
-        <x:v>0.07</x:v>
-      </x:c>
-      <x:c r="E21" s="306" t="n">
-        <x:v>0.015</x:v>
-      </x:c>
-      <x:c r="F21" s="306" t="n">
+        <x:v>0.056</x:v>
+      </x:c>
+      <x:c r="E21" s="306">
+        <x:f>'Weight_Evidence_2026-10-30'!F64/1000</x:f>
+        <x:v>0.014</x:v>
+      </x:c>
+      <x:c r="F21" s="306">
         <x:f>B21*E21</x:f>
-        <x:v>0.06</x:v>
-      </x:c>
-      <x:c r="G21" s="306" t="n">
+        <x:v>0.056</x:v>
+      </x:c>
+      <x:c r="G21" s="306">
         <x:f>D21-F21</x:f>
-        <x:v>0.010000000000000009</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H21" s="301" t="str">
         <x:v>CAD direct / link CAD report</x:v>
@@ -3313,26 +3340,26 @@
       </x:c>
       <x:c r="B22" s="317"/>
       <x:c r="C22" s="318"/>
-      <x:c r="D22" s="318" t="n">
+      <x:c r="D22" s="318">
         <x:f>SUM(D17:D21)</x:f>
-        <x:v>2.4799999999999995</x:v>
+        <x:v>2.928</x:v>
       </x:c>
       <x:c r="E22" s="318"/>
-      <x:c r="F22" s="318" t="n">
+      <x:c r="F22" s="318">
         <x:f>SUM(F17:F21)</x:f>
-        <x:v>2.3893999999999997</x:v>
-      </x:c>
-      <x:c r="G22" s="318" t="n">
+        <x:v>2.9432</x:v>
+      </x:c>
+      <x:c r="G22" s="318">
         <x:f>D22-F22</x:f>
-        <x:v>0.09059999999999979</x:v>
+        <x:v>-0.015200000000000102</x:v>
       </x:c>
       <x:c r="H22" s="317" t="str">
-        <x:v>Reconciled</x:v>
+        <x:v>Residual 9 g vs assembly</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="322" t="str">
-        <x:v>Interpretation: the 2.480 kg URDF baseline is internally CAD-consistent. The 2.297 kg physical weighing differs by 0.183 kg; the supplied inputs do not allocate that difference link by link, so no global inertia scaling has been applied. Create a separate configuration only after weighing the installed hardware with an explicit component inventory.</x:v>
+        <x:v>Interpretation: the 17 per-link masses sum to 2.928 kg; the Solid Edge assembly reports 2.937 kg. The 9 g residual is NOT missing geometry (the 17 link volumes close on the assembly volume within 1.1 mm³). It lies at the 1 g resolution of the mass reports: rounding of the 5 distinct reported masses explains at most ±8.5 g if the four legs are identical, so 9 g exceeds that bound by 0.5 g — either truncation instead of rounding, or legs not exactly identical in mass; it cannot be resolved without per-link reports of RF/RH/LH or unrounded values. No mass is added or scaled. The measured robot (2.807 kg, no Jetson) is 45 g above the CAD assembly without Jetson (2.762 kg); the weight workbook attributes 38.8 g to unmodeled wiring, which is a hypothesis.</x:v>
       </x:c>
       <x:c r="B24" s="322"/>
       <x:c r="C24" s="322"/>
@@ -3372,7 +3399,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="289" t="str">
-        <x:v>MATDOG — Metodo di conversione CAD → URDF &lt;inertial&gt;</x:v>
+        <x:v>MATDOG — Metodo di conversione CAD → URDF &lt;inertial&gt; (REV01-FIX)</x:v>
       </x:c>
       <x:c r="B1" s="289"/>
       <x:c r="C1" s="289"/>
@@ -3397,7 +3424,7 @@
         <x:v>1. Data scope</x:v>
       </x:c>
       <x:c r="B5" s="301" t="str">
-        <x:v>Base link and LF subassemblies were exported from Solid Edge. The CAD report prints CoM coordinates, principal-axis directions and radii of gyration. The full robot assembly report is used only as an aggregate validation.</x:v>
+        <x:v>1. Data scope — Base link and LF subassemblies were exported from Solid Edge on 2026-10-30 in the single nominal configuration that includes the Jetson Orin. Each report prints the CoM, principal-axis directions and radii of gyration. Moments 'rispetto agli assi globali' are about the CAD origin, NOT the CoM: they are used only as a cross-check. The full assembly report is an aggregate validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3405,7 +3432,7 @@
         <x:v>2. Mass source</x:v>
       </x:c>
       <x:c r="B6" s="301" t="str">
-        <x:v>URDF masses use the higher-precision CAD values from weight_breakdown_summary.txt: base 1.282 kg, hip 0.050 kg, upper 0.1725 kg, lower 0.0595 kg and foot 0.0175 kg. These sum to 2.480 kg.</x:v>
+        <x:v>2. Mass source — URDF masses are the Solid Edge per-link values (1 g resolution): base 1.828 kg, hip 0.050 kg, upper 0.152 kg, lower 0.059 kg and foot 0.014 kg; 17 links = 2.928 kg. The assembly reports 2.937 kg; the 9 g residual is documented in Mass_Reconciliation and not forced.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3413,7 +3440,7 @@
         <x:v>3. CoM source</x:v>
       </x:c>
       <x:c r="B7" s="301" t="str">
-        <x:v>Each direct CAD report provides the link CoM in millimetres. The values are converted to metres and used as &lt;inertial&gt;&lt;origin xyz=...&gt;.</x:v>
+        <x:v>3. CoM source — The CoM of each report (mm) is converted to metres and used as &lt;inertial&gt;&lt;origin xyz=...&gt; in the link frame (the report frame equals the URDF link frame, verified against the REV00 hip CoM).</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3421,7 +3448,7 @@
         <x:v>4. Inertia construction</x:v>
       </x:c>
       <x:c r="B8" s="301" t="str">
-        <x:v>The direct global-origin inertia entries are rounded in the text exports. To avoid parallel-axis rounding loss, the final inertia tensor is reconstructed at the CoM from principal axes and radii of gyration: I_C = Rᵀ diag(m·K₁², m·K₂², m·K₃²) R.</x:v>
+        <x:v>4. Inertia construction — The tensor at the CoM is rebuilt from principal axes and radii of gyration: I_C = Rᵀ diag(m·K₁², m·K₂², m·K₃²) R (units mm, kg·dm² converted to m, kg·m²). Check: the rebuilt tensors moved to the CAD origin reproduce the printed moments within the report rounding (diagonal error ≤ 4.4e-6 kg·m², i.e. below the 5e-6 rounding of 0.0005 kg·dm²). A printed '0.000' (foot) is a rounded small value, not zero inertia.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3429,7 +3456,7 @@
         <x:v>5. Axis cleanup</x:v>
       </x:c>
       <x:c r="B9" s="301" t="str">
-        <x:v>The exported principal-axis vectors are rounded to three decimals. Each 3×3 direction-cosine matrix is orthonormalized to the nearest right-handed rotation before tensor reconstruction.</x:v>
+        <x:v>5. Axis cleanup — The printed principal-axis matrices (3 decimals) are orthonormalised to the nearest rotation by SVD before the reconstruction (orthogonality error ≤ 9e-4 before cleanup).</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3437,7 +3464,7 @@
         <x:v>6. Right-side derivation</x:v>
       </x:c>
       <x:c r="B10" s="301" t="str">
-        <x:v>RF and RH hip/upper/lower properties are produced by local Y reflection: M = diag(1, −1, 1); CoM' = M·CoM and I' = M·I·Mᵀ.</x:v>
+        <x:v>6. Right-side derivation — RF = local Y reflection of LF: M = diag(1,−1,1); CoM' = M·CoM, I' = M·I·Mᵀ. Verified on the collision meshes: RF vs reflected LF differs by ≤ 0.0002 mm in CoM and ≤ 8e-6 relative in inertia for hip, upper and lower leg.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -3445,7 +3472,7 @@
         <x:v>7. Rear / foot derivation</x:v>
       </x:c>
       <x:c r="B11" s="301" t="str">
-        <x:v>LH uses the same left-side local geometry as LF. The CAD foot geometry is identical for all four legs; the LF foot tensor is reused. The aggregate assembly check validates these substitutions.</x:v>
+        <x:v>7. Rear / foot derivation — LH uses the LF frame (upper, lower and foot meshes identical to numerical precision); RH = Y reflection (upper, lower exact). The rear HIP collision meshes differ slightly from the front ones (volume −0.35 %, CoM 0.21 mm, inertia 0.8 % on the mesh estimate): rear hips inherit the LF CAD properties, an uncertainty below the 1 g mass resolution (2 %). Feet are identical.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -3453,7 +3480,7 @@
         <x:v>8. Aggregate validation</x:v>
       </x:c>
       <x:c r="B12" s="301" t="str">
-        <x:v>Rebuilt 17-link model: 2.480 kg, CoM = [9.571, −0.336, 5.970] mm. CAD assembly: 2.480 kg, CoM = [9.480, −0.710, 5.910] mm. Largest CoM deviation is 0.374 mm.</x:v>
+        <x:v>8. Aggregate validation — Rebuilt 17-link model: 2.928 kg, CoM = [0.688, −0.275, 17.286] mm, K = [115.39, 106.76, 73.74] mm. Solid Edge assembly (frame Base): 2.937 kg, CoM = [0.78, −0.59, 17.02] mm, K = [115.56, 106.96, 73.98] mm. CoM deviation 0.42 mm; principal moments within 1 %.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3461,7 +3488,7 @@
         <x:v>9. Product-of-inertia convention</x:v>
       </x:c>
       <x:c r="B13" s="301" t="str">
-        <x:v>Solid Edge lists products of inertia. URDF &lt;inertia&gt; uses tensor off-diagonal entries; the assembly principal-axis check validates the sign used in the reconstructed tensor. The final values stored in Inertial_Properties are the actual tensor entries.</x:v>
+        <x:v>9. Product-of-inertia convention — The printed products are ∫xy dm etc.; the URDF tensor off-diagonals are their negatives. Verified on the base_link (printed Ixz −0.021 kg·dm² ⇔ tensor +2.07e-4 kg·m²).</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -3469,7 +3496,7 @@
         <x:v>10. Neck yaw actuator</x:v>
       </x:c>
       <x:c r="B14" s="301" t="str">
-        <x:v>The provided assembly-scope note says the neck yaw actuator is not included as a standalone modeled component. REV00 remains 17 links and does not add an unlocated 0.061 kg mass. Add it only after exporting its mounted CAD subassembly or creating a fixed neck link.</x:v>
+        <x:v>10. Neck yaw actuator — No new evidence in the 2026-10-30 package; nothing is added. Whether the base_link CAD includes a fifth motor housing is not stated.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -3477,7 +3504,7 @@
         <x:v>11. Simulation scope</x:v>
       </x:c>
       <x:c r="B15" s="301" t="str">
-        <x:v>The resulting URDF is suitable for future rigid-body simulation of the 17-link CAD configuration. Current external-power/no-battery hardware should be represented by a separate configuration rather than modifying this CAD baseline ad hoc.</x:v>
+        <x:v>11. Simulation scope — A single nominal configuration, including the Jetson Orin. The robot weighed on 2026-10-30 (2.807 kg, without Jetson) is historical evidence of the hardware assembled at that date, not a second configuration. No dynamic hardware validation has been performed on these properties.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3486,6 +3513,1851 @@
     <x:mergeCell ref="A2:C2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF1E11D8-8308-4658-B391-A90E45E29188}">
+  <dimension ref="A1:N71"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="257" max="257" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="258" max="258" width="32" bestFit="1" customWidth="1"/>
+    <col min="265" max="265" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="513" max="513" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="514" max="514" width="32" bestFit="1" customWidth="1"/>
+    <col min="521" max="521" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="769" max="769" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="770" max="770" width="32" bestFit="1" customWidth="1"/>
+    <col min="777" max="777" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1025" max="1025" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1026" max="1026" width="32" bestFit="1" customWidth="1"/>
+    <col min="1033" max="1033" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1281" max="1281" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1282" max="1282" width="32" bestFit="1" customWidth="1"/>
+    <col min="1289" max="1289" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1537" max="1537" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1538" max="1538" width="32" bestFit="1" customWidth="1"/>
+    <col min="1545" max="1545" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1793" max="1793" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1794" max="1794" width="32" bestFit="1" customWidth="1"/>
+    <col min="1801" max="1801" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2049" max="2049" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2050" max="2050" width="32" bestFit="1" customWidth="1"/>
+    <col min="2057" max="2057" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2305" max="2305" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2306" max="2306" width="32" bestFit="1" customWidth="1"/>
+    <col min="2313" max="2313" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2561" max="2561" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2562" max="2562" width="32" bestFit="1" customWidth="1"/>
+    <col min="2569" max="2569" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2817" max="2817" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2818" max="2818" width="32" bestFit="1" customWidth="1"/>
+    <col min="2825" max="2825" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3073" max="3073" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3074" max="3074" width="32" bestFit="1" customWidth="1"/>
+    <col min="3081" max="3081" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3329" max="3329" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3330" max="3330" width="32" bestFit="1" customWidth="1"/>
+    <col min="3337" max="3337" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3585" max="3585" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3586" max="3586" width="32" bestFit="1" customWidth="1"/>
+    <col min="3593" max="3593" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3841" max="3841" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3842" max="3842" width="32" bestFit="1" customWidth="1"/>
+    <col min="3849" max="3849" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4097" max="4097" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="4098" max="4098" width="32" bestFit="1" customWidth="1"/>
+    <col min="4105" max="4105" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4353" max="4353" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="4354" max="4354" width="32" bestFit="1" customWidth="1"/>
+    <col min="4361" max="4361" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4609" max="4609" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="4610" max="4610" width="32" bestFit="1" customWidth="1"/>
+    <col min="4617" max="4617" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4865" max="4865" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="4866" max="4866" width="32" bestFit="1" customWidth="1"/>
+    <col min="4873" max="4873" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="5121" max="5121" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5122" max="5122" width="32" bestFit="1" customWidth="1"/>
+    <col min="5129" max="5129" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="5377" max="5377" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5378" max="5378" width="32" bestFit="1" customWidth="1"/>
+    <col min="5385" max="5385" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="5633" max="5633" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5634" max="5634" width="32" bestFit="1" customWidth="1"/>
+    <col min="5641" max="5641" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="5889" max="5889" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5890" max="5890" width="32" bestFit="1" customWidth="1"/>
+    <col min="5897" max="5897" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6145" max="6145" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6146" max="6146" width="32" bestFit="1" customWidth="1"/>
+    <col min="6153" max="6153" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6401" max="6401" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6402" max="6402" width="32" bestFit="1" customWidth="1"/>
+    <col min="6409" max="6409" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6657" max="6657" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6658" max="6658" width="32" bestFit="1" customWidth="1"/>
+    <col min="6665" max="6665" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="6913" max="6913" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6914" max="6914" width="32" bestFit="1" customWidth="1"/>
+    <col min="6921" max="6921" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7169" max="7169" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="7170" max="7170" width="32" bestFit="1" customWidth="1"/>
+    <col min="7177" max="7177" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7425" max="7425" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="7426" max="7426" width="32" bestFit="1" customWidth="1"/>
+    <col min="7433" max="7433" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7681" max="7681" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="7682" max="7682" width="32" bestFit="1" customWidth="1"/>
+    <col min="7689" max="7689" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7937" max="7937" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="7938" max="7938" width="32" bestFit="1" customWidth="1"/>
+    <col min="7945" max="7945" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="8193" max="8193" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="8194" max="8194" width="32" bestFit="1" customWidth="1"/>
+    <col min="8201" max="8201" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="8449" max="8449" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="8450" max="8450" width="32" bestFit="1" customWidth="1"/>
+    <col min="8457" max="8457" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="8705" max="8705" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="8706" max="8706" width="32" bestFit="1" customWidth="1"/>
+    <col min="8713" max="8713" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="8961" max="8961" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="8962" max="8962" width="32" bestFit="1" customWidth="1"/>
+    <col min="8969" max="8969" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="9217" max="9217" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="9218" max="9218" width="32" bestFit="1" customWidth="1"/>
+    <col min="9225" max="9225" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="9473" max="9473" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="9474" max="9474" width="32" bestFit="1" customWidth="1"/>
+    <col min="9481" max="9481" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="9729" max="9729" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="9730" max="9730" width="32" bestFit="1" customWidth="1"/>
+    <col min="9737" max="9737" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="9985" max="9985" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="9986" max="9986" width="32" bestFit="1" customWidth="1"/>
+    <col min="9993" max="9993" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="10241" max="10241" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="10242" max="10242" width="32" bestFit="1" customWidth="1"/>
+    <col min="10249" max="10249" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="10497" max="10497" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="10498" max="10498" width="32" bestFit="1" customWidth="1"/>
+    <col min="10505" max="10505" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="10753" max="10753" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="10754" max="10754" width="32" bestFit="1" customWidth="1"/>
+    <col min="10761" max="10761" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="11009" max="11009" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="11010" max="11010" width="32" bestFit="1" customWidth="1"/>
+    <col min="11017" max="11017" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="11265" max="11265" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="11266" max="11266" width="32" bestFit="1" customWidth="1"/>
+    <col min="11273" max="11273" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="11521" max="11521" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="11522" max="11522" width="32" bestFit="1" customWidth="1"/>
+    <col min="11529" max="11529" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="11777" max="11777" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="11778" max="11778" width="32" bestFit="1" customWidth="1"/>
+    <col min="11785" max="11785" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="12033" max="12033" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="12034" max="12034" width="32" bestFit="1" customWidth="1"/>
+    <col min="12041" max="12041" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="12289" max="12289" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="12290" max="12290" width="32" bestFit="1" customWidth="1"/>
+    <col min="12297" max="12297" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="12545" max="12545" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="12546" max="12546" width="32" bestFit="1" customWidth="1"/>
+    <col min="12553" max="12553" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="12801" max="12801" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="12802" max="12802" width="32" bestFit="1" customWidth="1"/>
+    <col min="12809" max="12809" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="13057" max="13057" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="13058" max="13058" width="32" bestFit="1" customWidth="1"/>
+    <col min="13065" max="13065" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="13313" max="13313" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="13314" max="13314" width="32" bestFit="1" customWidth="1"/>
+    <col min="13321" max="13321" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="13569" max="13569" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="13570" max="13570" width="32" bestFit="1" customWidth="1"/>
+    <col min="13577" max="13577" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="13825" max="13825" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="13826" max="13826" width="32" bestFit="1" customWidth="1"/>
+    <col min="13833" max="13833" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="14081" max="14081" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="14082" max="14082" width="32" bestFit="1" customWidth="1"/>
+    <col min="14089" max="14089" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="14337" max="14337" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="14338" max="14338" width="32" bestFit="1" customWidth="1"/>
+    <col min="14345" max="14345" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="14593" max="14593" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="14594" max="14594" width="32" bestFit="1" customWidth="1"/>
+    <col min="14601" max="14601" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="14849" max="14849" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="14850" max="14850" width="32" bestFit="1" customWidth="1"/>
+    <col min="14857" max="14857" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="15105" max="15105" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="15106" max="15106" width="32" bestFit="1" customWidth="1"/>
+    <col min="15113" max="15113" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="15361" max="15361" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="15362" max="15362" width="32" bestFit="1" customWidth="1"/>
+    <col min="15369" max="15369" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="15617" max="15617" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="15618" max="15618" width="32" bestFit="1" customWidth="1"/>
+    <col min="15625" max="15625" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="15873" max="15873" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="15874" max="15874" width="32" bestFit="1" customWidth="1"/>
+    <col min="15881" max="15881" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="16129" max="16129" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="16130" max="16130" width="32" bestFit="1" customWidth="1"/>
+    <col min="16137" max="16137" width="13.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" t="str">
+        <v>group</v>
+      </c>
+      <c r="B1" t="str">
+        <v>part</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Unit.</v>
+      </c>
+      <c r="D1"/>
+      <c r="E1" t="str">
+        <v>Q.ty</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Tot.</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Source: 'Evidenze peso e calcoli.xlsx' (sha256 a3b1fc77e9d9b4d49b22714d9adae554e33155379f7c88815c30cfbdffda76a3), copied unchanged on 2026-10-31: values and formulas as supplied.</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B2" t="str">
+        <v>portafusibile+fusibile+cavi</v>
+      </c>
+      <c r="C2">
+        <v>12</v>
+      </c>
+      <c r="D2" t="str">
+        <v>g</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <f t="shared" ref="F2:F31" si="0">C2*E2</f>
+        <v>12</v>
+      </c>
+      <c r="G2" t="str">
+        <v>g</v>
+      </c>
+      <c r="I2" t="str">
+        <v>peso robot tot.</v>
+      </c>
+      <c r="J2">
+        <v>2807</v>
+      </c>
+      <c r="K2" t="str">
+        <v>g</v>
+      </c>
+      <c r="L2" t="str">
+        <v>(al 30/10/2026)</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B3" t="str">
+        <v>wifi_antenna (+ spinotto)</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3" t="str">
+        <v>g</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="G3" t="str">
+        <v>g</v>
+      </c>
+      <c r="I3" t="str">
+        <v>(senza jetson orin)</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B4" t="str">
+        <v>base_link__charge_pads_cover</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4" t="str">
+        <v>g</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G4" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B5" t="str">
+        <v>dado m4 flang</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="str">
+        <v>g</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G5" t="str">
+        <v>g</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Unit.</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Q.ty</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Tot.</v>
+      </c>
+      <c r="N5"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B6" t="str">
+        <v>occhiello m4+cavo</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6" t="str">
+        <v>g</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" t="str">
+        <v>g</v>
+      </c>
+      <c r="I6" t="str">
+        <v>servo cable+4xM2.5</v>
+      </c>
+      <c r="J6">
+        <f>J19</f>
+        <v>1.5</v>
+      </c>
+      <c r="K6" t="str">
+        <v>g</v>
+      </c>
+      <c r="L6">
+        <v>8</v>
+      </c>
+      <c r="M6">
+        <f>J6*L6</f>
+        <v>12</v>
+      </c>
+      <c r="N6" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B7" t="str">
+        <v>soldered_rear_pad</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7" t="str">
+        <v>g</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="G7" t="str">
+        <v>g</v>
+      </c>
+      <c r="I7" t="str">
+        <v>motor housing</v>
+      </c>
+      <c r="J7">
+        <v>58</v>
+      </c>
+      <c r="K7" t="str">
+        <v>g</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <f>J7*L7</f>
+        <v>290</v>
+      </c>
+      <c r="N7" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B8" t="str">
+        <v>magnete Ø3x6</v>
+      </c>
+      <c r="C8">
+        <v>0.5</v>
+      </c>
+      <c r="D8" t="str">
+        <v>g</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G8" t="str">
+        <v>g</v>
+      </c>
+      <c r="I8" t="str">
+        <v>zampa completa</v>
+      </c>
+      <c r="J8">
+        <f>F69</f>
+        <v>275.39999999999998</v>
+      </c>
+      <c r="K8" t="str">
+        <v>g</v>
+      </c>
+      <c r="L8">
+        <v>4</v>
+      </c>
+      <c r="M8">
+        <f>J8*L8</f>
+        <v>1101.5999999999999</v>
+      </c>
+      <c r="N8" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B9" t="str">
+        <v>vite M2.5 x 6 autof.</v>
+      </c>
+      <c r="C9">
+        <v>0.5</v>
+      </c>
+      <c r="D9" t="str">
+        <v>g</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G9" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B10" t="str">
+        <v>rear_fuse_cover (disgiuntore)</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+      <c r="D10" t="str">
+        <v>g</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="G10" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B11" t="str">
+        <v>base_link_rear</v>
+      </c>
+      <c r="C11">
+        <v>49</v>
+      </c>
+      <c r="D11" t="str">
+        <v>g</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="G11" t="str">
+        <v>g</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Somma CAD</v>
+      </c>
+      <c r="J11">
+        <f>F33-F16+SUM(M6:M8)</f>
+        <v>2768.2</v>
+      </c>
+      <c r="K11" t="str">
+        <v>g</v>
+      </c>
+      <c r="L11" t="str">
+        <v>(rimossa Jetson Orin)</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B12" t="str">
+        <v>vite M3.5 x 20 autof.</v>
+      </c>
+      <c r="C12">
+        <v>2.5</v>
+      </c>
+      <c r="D12" t="str">
+        <v>g</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G12" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B13" t="str">
+        <v>base_link__main_chassis</v>
+      </c>
+      <c r="C13">
+        <v>283</v>
+      </c>
+      <c r="D13" t="str">
+        <v>g</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>283</v>
+      </c>
+      <c r="G13" t="str">
+        <v>g</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Diff</v>
+      </c>
+      <c r="J13">
+        <f>J2-J11</f>
+        <v>38.800000000000182</v>
+      </c>
+      <c r="K13" t="str">
+        <v>g</v>
+      </c>
+      <c r="L13">
+        <f>1-J2/J11</f>
+        <v>-1.4016328299978342E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B14" t="str">
+        <v>base_link__body_cover</v>
+      </c>
+      <c r="C14">
+        <v>86</v>
+      </c>
+      <c r="D14" t="str">
+        <v>g</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="G14" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B15" t="str">
+        <v>base_link__battery_cover</v>
+      </c>
+      <c r="C15">
+        <v>41</v>
+      </c>
+      <c r="D15" t="str">
+        <v>g</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="G15" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B16" t="str">
+        <v>base_link__jetson_orin_nano</v>
+      </c>
+      <c r="C16">
+        <v>175</v>
+      </c>
+      <c r="D16" t="str">
+        <v>g</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>175</v>
+      </c>
+      <c r="G16" t="str">
+        <v>g</v>
+      </c>
+      <c r="I16" t="str">
+        <v>evidenze misurate</v>
+      </c>
+      <c r="J16"/>
+      <c r="K16"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B17" t="str">
+        <v>base_link__battery_3s_9000mah</v>
+      </c>
+      <c r="C17">
+        <v>561</v>
+      </c>
+      <c r="D17" t="str">
+        <v>g</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>561</v>
+      </c>
+      <c r="G17" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Adafruit_BNO085_STEMMA_QT</v>
+      </c>
+      <c r="C18">
+        <v>5</v>
+      </c>
+      <c r="D18" t="str">
+        <v>g</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G18" t="str">
+        <v>g</v>
+      </c>
+      <c r="I18" t="str">
+        <v>motor housing</v>
+      </c>
+      <c r="J18">
+        <v>58</v>
+      </c>
+      <c r="K18" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Daly_Smart_BMS_H-series_3S_60A</v>
+      </c>
+      <c r="C19">
+        <v>133</v>
+      </c>
+      <c r="D19" t="str">
+        <v>g</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>133</v>
+      </c>
+      <c r="G19" t="str">
+        <v>g</v>
+      </c>
+      <c r="I19" t="str">
+        <v>servo cable+4xM2.5</v>
+      </c>
+      <c r="J19">
+        <v>1.5</v>
+      </c>
+      <c r="K19" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B20" t="str">
+        <v>base_link__BMS_holder</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20" t="str">
+        <v>g</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G20" t="str">
+        <v>g</v>
+      </c>
+      <c r="I20" t="str">
+        <v>horn</v>
+      </c>
+      <c r="J20">
+        <v>2</v>
+      </c>
+      <c r="K20" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B21" t="str">
+        <v>motion_controller__bracket</v>
+      </c>
+      <c r="C21">
+        <v>9</v>
+      </c>
+      <c r="D21" t="str">
+        <v>g</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="G21" t="str">
+        <v>g</v>
+      </c>
+      <c r="I21" t="str">
+        <v>idler_horn</v>
+      </c>
+      <c r="J21">
+        <v>1.25</v>
+      </c>
+      <c r="K21" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B22" t="str">
+        <v>motion_controller__shield</v>
+      </c>
+      <c r="C22">
+        <v>21</v>
+      </c>
+      <c r="D22" t="str">
+        <v>g</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="G22" t="str">
+        <v>g</v>
+      </c>
+      <c r="I22" t="str">
+        <v>vite M3x6</v>
+      </c>
+      <c r="J22">
+        <v>0.7</v>
+      </c>
+      <c r="K22" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B23" t="str">
+        <v>ESP32_S3_WROOM</v>
+      </c>
+      <c r="C23">
+        <v>12</v>
+      </c>
+      <c r="D23" t="str">
+        <v>g</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="G23" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B24" t="str">
+        <v>led_ring_d38_WS2812</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24" t="str">
+        <v>g</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G24" t="str">
+        <v>g</v>
+      </c>
+      <c r="I24" t="str">
+        <v>hip_leg_link</v>
+      </c>
+      <c r="J24">
+        <v>31</v>
+      </c>
+      <c r="K24" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B25" t="str">
+        <v>key_toggle_switch</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" t="str">
+        <v>g</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G25" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B26" t="str">
+        <v>cover_led_logo</v>
+      </c>
+      <c r="C26">
+        <v>4</v>
+      </c>
+      <c r="D26" t="str">
+        <v>g</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G26" t="str">
+        <v>g</v>
+      </c>
+      <c r="I26" t="str">
+        <v>upper leg link</v>
+      </c>
+      <c r="J26">
+        <v>30</v>
+      </c>
+      <c r="K26" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B27" t="str">
+        <v>SEED_Bus_Servo_Driver_Board</v>
+      </c>
+      <c r="C27">
+        <v>10</v>
+      </c>
+      <c r="D27" t="str">
+        <v>g</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G27" t="str">
+        <v>g</v>
+      </c>
+      <c r="I27" t="str">
+        <v>upper leg cover</v>
+      </c>
+      <c r="J27">
+        <v>3</v>
+      </c>
+      <c r="K27" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B28" t="str">
+        <v>servo_power_board</v>
+      </c>
+      <c r="C28">
+        <v>32</v>
+      </c>
+      <c r="D28" t="str">
+        <v>g</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="G28" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B29" t="str">
+        <v>dado m4 flang</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="str">
+        <v>g</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G29" t="str">
+        <v>g</v>
+      </c>
+      <c r="I29" t="str">
+        <v>lower_leg_link</v>
+      </c>
+      <c r="J29">
+        <v>46.5</v>
+      </c>
+      <c r="K29" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B30" t="str">
+        <v>BT dongle Daly</v>
+      </c>
+      <c r="C30">
+        <v>28</v>
+      </c>
+      <c r="D30" t="str">
+        <v>g</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="G30" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="B31" t="str">
+        <v>viti autofilettanti (peso medio)</v>
+      </c>
+      <c r="C31">
+        <v>1.2</v>
+      </c>
+      <c r="D31" t="str">
+        <v>g</v>
+      </c>
+      <c r="E31">
+        <v>18</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>21.599999999999998</v>
+      </c>
+      <c r="G31" t="str">
+        <v>g</v>
+      </c>
+      <c r="I31" t="str">
+        <v>rubber_foot</v>
+      </c>
+      <c r="J31">
+        <v>6.5</v>
+      </c>
+      <c r="K31" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B33" t="str">
+        <v>Somma analitica Base_link senza motor joint x 5</v>
+      </c>
+      <c r="E33" t="str">
+        <v>sub. Tot.</v>
+      </c>
+      <c r="F33">
+        <f>SUM(F2:F31)</f>
+        <v>1539.6</v>
+      </c>
+      <c r="G33" t="str">
+        <v>gr</v>
+      </c>
+      <c r="I33" t="str">
+        <v>vite M5x12 TBEI</v>
+      </c>
+      <c r="J33">
+        <v>2.25</v>
+      </c>
+      <c r="K33" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I34" t="str">
+        <v>dado m5</v>
+      </c>
+      <c r="J34">
+        <v>1.5</v>
+      </c>
+      <c r="K34" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" t="str">
+        <v>group</v>
+      </c>
+      <c r="B36" t="str">
+        <v>part</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Unit.</v>
+      </c>
+      <c r="D36"/>
+      <c r="E36" t="str">
+        <v>Q.ty</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Tot.</v>
+      </c>
+      <c r="I36" t="str">
+        <v>base_link</v>
+      </c>
+      <c r="J36">
+        <v>283</v>
+      </c>
+      <c r="K36" t="str">
+        <v>g</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" t="str">
+        <v>*hip_leg_link</v>
+      </c>
+      <c r="B37" t="str">
+        <v>*_hip_link</v>
+      </c>
+      <c r="C37">
+        <f>J24</f>
+        <v>31</v>
+      </c>
+      <c r="D37" t="str">
+        <v>g</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <f>C37*E37</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" t="str">
+        <v>*hip_leg_link</v>
+      </c>
+      <c r="B38" t="str">
+        <v>horn</v>
+      </c>
+      <c r="C38">
+        <f>J20</f>
+        <v>2</v>
+      </c>
+      <c r="D38" t="str">
+        <v>g</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="F38">
+        <f t="shared" ref="F38:F40" si="1">C38*E38</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" t="str">
+        <v>*hip_leg_link</v>
+      </c>
+      <c r="B39" t="str">
+        <v>idler horn</v>
+      </c>
+      <c r="C39">
+        <f>J21</f>
+        <v>1.25</v>
+      </c>
+      <c r="D39" t="str">
+        <v>g</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" t="str">
+        <v>*hip_leg_link</v>
+      </c>
+      <c r="B40" t="str">
+        <v>vite M3x6</v>
+      </c>
+      <c r="C40">
+        <f>J22</f>
+        <v>0.7</v>
+      </c>
+      <c r="D40" t="str">
+        <v>g</v>
+      </c>
+      <c r="E40">
+        <v>18</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="1"/>
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E41" t="str">
+        <v>Tot. Analit.</v>
+      </c>
+      <c r="F41">
+        <f>SUM(F37:F40)</f>
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E42" t="str">
+        <v>Tot. CAD</v>
+      </c>
+      <c r="F42">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E43" t="str">
+        <v>% CAD</v>
+      </c>
+      <c r="F43">
+        <f>ABS(1-(F42/F41))</f>
+        <v>1.9960079840319889E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" t="str">
+        <v>*upper_leg_link</v>
+      </c>
+      <c r="B45" t="str">
+        <v>main__upper_leg_link</v>
+      </c>
+      <c r="C45">
+        <f>J26</f>
+        <v>30</v>
+      </c>
+      <c r="D45" t="str">
+        <v>g</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <f>C45*E45</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" t="str">
+        <v>*upper_leg_link</v>
+      </c>
+      <c r="B46" t="str">
+        <v>cover__upper_leg_link</v>
+      </c>
+      <c r="C46">
+        <f>J27</f>
+        <v>3</v>
+      </c>
+      <c r="D46" t="str">
+        <v>g</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46">
+        <f t="shared" ref="F46:F48" si="2">C46*E46</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" t="str">
+        <v>*upper_leg_link</v>
+      </c>
+      <c r="B47" t="str">
+        <v>joint__servo_ST3215_body</v>
+      </c>
+      <c r="C47">
+        <f>J18</f>
+        <v>58</v>
+      </c>
+      <c r="D47" t="str">
+        <v>g</v>
+      </c>
+      <c r="E47">
+        <v>2</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="2"/>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B48" t="str">
+        <v>motor cable</v>
+      </c>
+      <c r="C48">
+        <f>J19</f>
+        <v>1.5</v>
+      </c>
+      <c r="D48" t="str">
+        <v>g</v>
+      </c>
+      <c r="E48">
+        <v>2</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E49" t="str">
+        <v>Tot. Analit.</v>
+      </c>
+      <c r="F49">
+        <f>SUM(F45:F48)</f>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E50" t="str">
+        <v>Tot. CAD</v>
+      </c>
+      <c r="F50">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E51" t="str">
+        <v>% CAD</v>
+      </c>
+      <c r="F51">
+        <f>ABS(1-(F50/F49))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="str">
+        <v>*lower_leg_link</v>
+      </c>
+      <c r="B53" t="str">
+        <v>*_lower_leg_link</v>
+      </c>
+      <c r="C53">
+        <f>J29</f>
+        <v>46.5</v>
+      </c>
+      <c r="D53" t="str">
+        <v>g</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <f>C53*E53</f>
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="str">
+        <v>*lower_leg_link</v>
+      </c>
+      <c r="B54" t="str">
+        <v>horn</v>
+      </c>
+      <c r="C54">
+        <f>J20</f>
+        <v>2</v>
+      </c>
+      <c r="D54" t="str">
+        <v>g</v>
+      </c>
+      <c r="E54">
+        <v>2</v>
+      </c>
+      <c r="F54">
+        <f t="shared" ref="F54:F56" si="3">C54*E54</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="str">
+        <v>*lower_leg_link</v>
+      </c>
+      <c r="B55" t="str">
+        <v>idler horn</v>
+      </c>
+      <c r="C55">
+        <f>J21</f>
+        <v>1.25</v>
+      </c>
+      <c r="D55" t="str">
+        <v>g</v>
+      </c>
+      <c r="E55">
+        <v>2</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="3"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="str">
+        <v>*lower_leg_link</v>
+      </c>
+      <c r="B56" t="str">
+        <v>vite M3x6</v>
+      </c>
+      <c r="C56">
+        <f>J22</f>
+        <v>0.7</v>
+      </c>
+      <c r="D56" t="str">
+        <v>g</v>
+      </c>
+      <c r="E56">
+        <v>9</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="3"/>
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E57" t="str">
+        <v>Tot. Analit.</v>
+      </c>
+      <c r="F57">
+        <f>SUM(F53:F56)</f>
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E58" t="str">
+        <v>Tot. CAD</v>
+      </c>
+      <c r="F58">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E59" t="str">
+        <v>% CAD</v>
+      </c>
+      <c r="F59">
+        <f>ABS(1-(F58/F57))</f>
+        <v>5.0590219224282418E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="str">
+        <v>*foot_leg_link</v>
+      </c>
+      <c r="B61" t="str">
+        <v>*_feet_leg_link</v>
+      </c>
+      <c r="C61">
+        <f>J31</f>
+        <v>6.5</v>
+      </c>
+      <c r="D61" t="str">
+        <v>g</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61">
+        <f>C61*E61</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="str">
+        <v>*foot_leg_link</v>
+      </c>
+      <c r="B62" t="str">
+        <v>vite M5x12 TBEI</v>
+      </c>
+      <c r="C62">
+        <f>J33</f>
+        <v>2.25</v>
+      </c>
+      <c r="D62" t="str">
+        <v>g</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
+      </c>
+      <c r="F62">
+        <f t="shared" ref="F62:F63" si="4">C62*E62</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="str">
+        <v>*foot_leg_link</v>
+      </c>
+      <c r="B63" t="str">
+        <v>dado m5</v>
+      </c>
+      <c r="C63">
+        <f>J34</f>
+        <v>1.5</v>
+      </c>
+      <c r="D63" t="str">
+        <v>g</v>
+      </c>
+      <c r="E63">
+        <v>2</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B64"/>
+      <c r="E64" t="str">
+        <v>Tot. Analit.</v>
+      </c>
+      <c r="F64">
+        <f>SUM(F61:F63)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E65" t="str">
+        <v>Tot. CAD</v>
+      </c>
+      <c r="F65">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E66" t="str">
+        <v>% CAD</v>
+      </c>
+      <c r="F66">
+        <f>ABS(1-(F65/F64))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E68" t="str">
+        <v>TOTALE ZAMPA</v>
+      </c>
+      <c r="F68"/>
+    </row>
+    <row r="69" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E69" t="str">
+        <v>Tot. Analit.</v>
+      </c>
+      <c r="F69">
+        <f>SUM(F41+F49+F57+F64)</f>
+        <v>275.39999999999998</v>
+      </c>
+    </row>
+    <row r="70" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E70" t="str">
+        <v>Tot. CAD</v>
+      </c>
+      <c r="F70">
+        <f>SUM(F42+F50+F58+F65)</f>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="71" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E71" t="str">
+        <v>% CAD</v>
+      </c>
+      <c r="F71">
+        <f>ABS(1-(F70/F69))</f>
+        <v>1.4524328249817531E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I16:K16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:cols>
+    <x:col min="1" max="1" width="52" customWidth="1"/>
+    <x:col min="2" max="2" width="70" customWidth="1"/>
+    <x:col min="3" max="3" width="14" customWidth="1"/>
+    <x:col min="4" max="4" width="60" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str" s="345">
+        <x:v>Evidence file</x:v>
+      </x:c>
+      <x:c r="B1" t="str" s="345">
+        <x:v>SHA-256</x:v>
+      </x:c>
+      <x:c r="C1" t="str" s="345">
+        <x:v>Role</x:v>
+      </x:c>
+      <x:c r="D1" t="str" s="345">
+        <x:v>Location</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str" s="372">
+        <x:v>Evidenze peso e calcoli.xlsx</x:v>
+      </x:c>
+      <x:c r="B2" t="str" s="372">
+        <x:v>a3b1fc77e9d9b4d49b22714d9adae554e33155379f7c88815c30cfbdffda76a3</x:v>
+      </x:c>
+      <x:c r="C2" t="str" s="372">
+        <x:v>CURRENT</x:v>
+      </x:c>
+      <x:c r="D2" t="str" s="372">
+        <x:v>09_Logs/Validation_Reports/REV01_FIX_Physical_Properties_2026-10-31/input/Evidenze peso e calcoli.xlsx</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str" s="372">
+        <x:v>PESO REALE DEL ROBOT AL 30_10_2026.docx</x:v>
+      </x:c>
+      <x:c r="B3" t="str" s="372">
+        <x:v>9eda346ccf028afab08fac93ebca437d3414376b8ea3317508fdbde399c16b09</x:v>
+      </x:c>
+      <x:c r="C3" t="str" s="372">
+        <x:v>CURRENT</x:v>
+      </x:c>
+      <x:c r="D3" t="str" s="372">
+        <x:v>09_Logs/Validation_Reports/REV01_FIX_Physical_Properties_2026-10-31/input/PESO REALE DEL ROBOT AL 30_10_2026.docx</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str" s="372">
+        <x:v>base_link__physprop.txt</x:v>
+      </x:c>
+      <x:c r="B4" t="str" s="372">
+        <x:v>5aac79cfb3f1ecd0ad2be7f4a789e76b44b348e8c5bd28c9a4b9c809e3e489a0</x:v>
+      </x:c>
+      <x:c r="C4" t="str" s="372">
+        <x:v>CURRENT</x:v>
+      </x:c>
+      <x:c r="D4" t="str" s="372">
+        <x:v>09_Logs/Validation_Reports/REV01_FIX_Physical_Properties_2026-10-31/input/base_link__physprop.txt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str" s="372">
+        <x:v>matdog_urdf_assembly__physprop.txt</x:v>
+      </x:c>
+      <x:c r="B5" t="str" s="372">
+        <x:v>cc3bc10bfd358d77d937cd4590574b75bb8fb6cdcef4329073f3a0efb7c0c53c</x:v>
+      </x:c>
+      <x:c r="C5" t="str" s="372">
+        <x:v>CURRENT</x:v>
+      </x:c>
+      <x:c r="D5" t="str" s="372">
+        <x:v>09_Logs/Validation_Reports/REV01_FIX_Physical_Properties_2026-10-31/input/matdog_urdf_assembly__physprop.txt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str" s="372">
+        <x:v>lf_hip_link__physprop.txt</x:v>
+      </x:c>
+      <x:c r="B6" t="str" s="372">
+        <x:v>79b12a9aaccc08979f0640053c362a75ee953223bf83ca9490be052f3a2354f5</x:v>
+      </x:c>
+      <x:c r="C6" t="str" s="372">
+        <x:v>CURRENT</x:v>
+      </x:c>
+      <x:c r="D6" t="str" s="372">
+        <x:v>09_Logs/Validation_Reports/REV01_FIX_Physical_Properties_2026-10-31/input/lf_hip_link__physprop.txt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str" s="372">
+        <x:v>lf_upper_leg_link__physprop.txt</x:v>
+      </x:c>
+      <x:c r="B7" t="str" s="372">
+        <x:v>70cc00fcafe6d370dfdacc68f9d9437646ae3356e532fc9e7f364ac07749c597</x:v>
+      </x:c>
+      <x:c r="C7" t="str" s="372">
+        <x:v>CURRENT</x:v>
+      </x:c>
+      <x:c r="D7" t="str" s="372">
+        <x:v>09_Logs/Validation_Reports/REV01_FIX_Physical_Properties_2026-10-31/input/lf_upper_leg_link__physprop.txt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str" s="372">
+        <x:v>lf_lower_leg_link__physprop.txt</x:v>
+      </x:c>
+      <x:c r="B8" t="str" s="372">
+        <x:v>039eeb8b54c65f1a63d119438277ecea01a89b0ceaed86af02ed96f7963381b5</x:v>
+      </x:c>
+      <x:c r="C8" t="str" s="372">
+        <x:v>CURRENT</x:v>
+      </x:c>
+      <x:c r="D8" t="str" s="372">
+        <x:v>09_Logs/Validation_Reports/REV01_FIX_Physical_Properties_2026-10-31/input/lf_lower_leg_link__physprop.txt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str" s="372">
+        <x:v>lf_foot_link__physprop.txt</x:v>
+      </x:c>
+      <x:c r="B9" t="str" s="372">
+        <x:v>cd976bbcde4d48d2b3628fe59017be7ff68a23cce938551b20941a3678ca67fd</x:v>
+      </x:c>
+      <x:c r="C9" t="str" s="372">
+        <x:v>CURRENT</x:v>
+      </x:c>
+      <x:c r="D9" t="str" s="372">
+        <x:v>09_Logs/Validation_Reports/REV01_FIX_Physical_Properties_2026-10-31/input/lf_foot_link__physprop.txt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str" s="372">
+        <x:v>Coordinate_Cinematiche_matt_robodog_rev00.xlsx (before the 2026-10-31 update)</x:v>
+      </x:c>
+      <x:c r="B10" t="str" s="372">
+        <x:v>381675b4c4fae0305ed2a2e882c0b9b43f513d9f0e53afff41e60801d798b13f</x:v>
+      </x:c>
+      <x:c r="C10" t="str" s="372">
+        <x:v>HISTORICAL (Git)</x:v>
+      </x:c>
+      <x:c r="D10" t="str" s="372">
+        <x:v>git show 0f8f7ff:03_CAD/URDF/matt_robodog_rev00/reference/Coordinate_Cinematiche_matt_robodog_rev00.xlsx</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str" s="372">
+        <x:v>REV00 physical-property reports (physprop__*.txt, weight_breakdown_summary.txt)</x:v>
+      </x:c>
+      <x:c r="B11" t="str" s="372">
+        <x:v>not in the repository; their values were transcribed in the superseded sheets of the previous workbook version</x:v>
+      </x:c>
+      <x:c r="C11" t="str" s="372">
+        <x:v>HISTORICAL (Git)</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
 </x:worksheet>
 </file>
 
@@ -3555,7 +5427,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="399" t="str">
-        <x:v>Origini mesh visual/collision: xyz = 0,0,0 m · rpy = 0°,0°,0°. Gli STL CAD restano in millimetri; ogni &lt;mesh&gt; URDF applica scale="0.001 0.001 0.001".</x:v>
+        <x:v>Origini mesh visual/collision: xyz = 0,0,0 m · rpy = 0°,0°,0°. Visual e collision usano la stessa STL per link (meshes/collision/&lt;link&gt;.stl, REV01-FIX). Gli STL CAD restano in millimetri; ogni &lt;mesh&gt; URDF applica scale="0.001 0.001 0.001". Le masse sono lette da Inertial_Properties.</x:v>
       </x:c>
       <x:c r="B2" s="399"/>
       <x:c r="C2" s="399"/>
@@ -3688,10 +5560,10 @@
         <x:v>base_link</x:v>
       </x:c>
       <x:c r="B6" s="359" t="str">
-        <x:v>meshes/base_link.stl</x:v>
+        <x:v>meshes/collision/base_link.stl</x:v>
       </x:c>
       <x:c r="C6" s="359" t="str">
-        <x:v>meshes/base_link.stl</x:v>
+        <x:v>meshes/collision/base_link.stl</x:v>
       </x:c>
       <x:c r="D6" s="360" t="n">
         <x:v>0</x:v>
@@ -3729,17 +5601,19 @@
       <x:c r="O6" s="361" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P6" s="306" t="n">
-        <x:v>1282</x:v>
-      </x:c>
-      <x:c r="Q6" s="306" t="n">
-        <x:v>1.282</x:v>
+      <x:c r="P6" s="306">
+        <x:f>Q6*1000</x:f>
+        <x:v>1828</x:v>
+      </x:c>
+      <x:c r="Q6" s="306">
+        <x:f>Inertial_Properties!D5</x:f>
+        <x:v>1.828</x:v>
       </x:c>
       <x:c r="R6" s="301" t="str">
         <x:v>CAD physical-property report</x:v>
       </x:c>
       <x:c r="S6" s="301" t="str">
-        <x:v>physprop__base_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>base_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="T6" s="301" t="str">
         <x:v>CoM available</x:v>
@@ -3771,10 +5645,10 @@
         <x:v>lf_hip_link</x:v>
       </x:c>
       <x:c r="B7" s="359" t="str">
-        <x:v>meshes/lf_hip_link.stl</x:v>
+        <x:v>meshes/collision/lf_hip_link.stl</x:v>
       </x:c>
       <x:c r="C7" s="359" t="str">
-        <x:v>meshes/lf_hip_link.stl</x:v>
+        <x:v>meshes/collision/lf_hip_link.stl</x:v>
       </x:c>
       <x:c r="D7" s="360" t="n">
         <x:v>0</x:v>
@@ -3812,17 +5686,19 @@
       <x:c r="O7" s="361" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P7" s="306" t="n">
+      <x:c r="P7" s="306">
+        <x:f>Q7*1000</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="Q7" s="306" t="n">
+      <x:c r="Q7" s="306">
+        <x:f>Inertial_Properties!D6</x:f>
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="R7" s="301" t="str">
         <x:v>CAD physical-property report</x:v>
       </x:c>
       <x:c r="S7" s="301" t="str">
-        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_hip_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="T7" s="301" t="str">
         <x:v>CoM available</x:v>
@@ -3854,10 +5730,10 @@
         <x:v>lf_upper_leg_link</x:v>
       </x:c>
       <x:c r="B8" s="362" t="str">
-        <x:v>meshes/lf_upper_leg_link.stl</x:v>
+        <x:v>meshes/collision/lf_upper_leg_link.stl</x:v>
       </x:c>
       <x:c r="C8" s="362" t="str">
-        <x:v>meshes/lf_upper_leg_link.stl</x:v>
+        <x:v>meshes/collision/lf_upper_leg_link.stl</x:v>
       </x:c>
       <x:c r="D8" s="363" t="n">
         <x:v>0</x:v>
@@ -3895,17 +5771,19 @@
       <x:c r="O8" s="364" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P8" s="306" t="n">
-        <x:v>172.5</x:v>
-      </x:c>
-      <x:c r="Q8" s="306" t="n">
-        <x:v>0.1725</x:v>
+      <x:c r="P8" s="306">
+        <x:f>Q8*1000</x:f>
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="Q8" s="306">
+        <x:f>Inertial_Properties!D7</x:f>
+        <x:v>0.152</x:v>
       </x:c>
       <x:c r="R8" s="301" t="str">
         <x:v>CAD physical-property report</x:v>
       </x:c>
       <x:c r="S8" s="301" t="str">
-        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_upper_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="T8" s="301" t="str">
         <x:v>CoM available</x:v>
@@ -3937,10 +5815,10 @@
         <x:v>lf_lower_leg_link</x:v>
       </x:c>
       <x:c r="B9" s="359" t="str">
-        <x:v>meshes/lf_lower_leg_link.stl</x:v>
+        <x:v>meshes/collision/lf_lower_leg_link.stl</x:v>
       </x:c>
       <x:c r="C9" s="359" t="str">
-        <x:v>meshes/lf_lower_leg_link.stl</x:v>
+        <x:v>meshes/collision/lf_lower_leg_link.stl</x:v>
       </x:c>
       <x:c r="D9" s="360" t="n">
         <x:v>0</x:v>
@@ -3978,17 +5856,19 @@
       <x:c r="O9" s="361" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P9" s="306" t="n">
-        <x:v>59.5</x:v>
-      </x:c>
-      <x:c r="Q9" s="306" t="n">
-        <x:v>0.0595</x:v>
+      <x:c r="P9" s="306">
+        <x:f>Q9*1000</x:f>
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="Q9" s="306">
+        <x:f>Inertial_Properties!D8</x:f>
+        <x:v>0.059</x:v>
       </x:c>
       <x:c r="R9" s="301" t="str">
         <x:v>CAD physical-property report</x:v>
       </x:c>
       <x:c r="S9" s="301" t="str">
-        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_lower_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="T9" s="301" t="str">
         <x:v>CoM available</x:v>
@@ -4020,10 +5900,10 @@
         <x:v>lf_foot_link</x:v>
       </x:c>
       <x:c r="B10" s="359" t="str">
-        <x:v>meshes/lf_foot_link.stl</x:v>
+        <x:v>meshes/collision/lf_foot_link.stl</x:v>
       </x:c>
       <x:c r="C10" s="359" t="str">
-        <x:v>meshes/lf_foot_link.stl</x:v>
+        <x:v>meshes/collision/lf_foot_link.stl</x:v>
       </x:c>
       <x:c r="D10" s="360" t="n">
         <x:v>0</x:v>
@@ -4061,17 +5941,19 @@
       <x:c r="O10" s="361" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P10" s="306" t="n">
-        <x:v>17.5</x:v>
-      </x:c>
-      <x:c r="Q10" s="306" t="n">
-        <x:v>0.0175</x:v>
+      <x:c r="P10" s="306">
+        <x:f>Q10*1000</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q10" s="306">
+        <x:f>Inertial_Properties!D9</x:f>
+        <x:v>0.014</x:v>
       </x:c>
       <x:c r="R10" s="301" t="str">
         <x:v>CAD physical-property report</x:v>
       </x:c>
       <x:c r="S10" s="301" t="str">
-        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_foot_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="T10" s="301" t="str">
         <x:v>CoM available</x:v>
@@ -4103,10 +5985,10 @@
         <x:v>rf_hip_link</x:v>
       </x:c>
       <x:c r="B11" s="359" t="str">
-        <x:v>meshes/rf_hip_link.stl</x:v>
+        <x:v>meshes/collision/rf_hip_link.stl</x:v>
       </x:c>
       <x:c r="C11" s="359" t="str">
-        <x:v>meshes/rf_hip_link.stl</x:v>
+        <x:v>meshes/collision/rf_hip_link.stl</x:v>
       </x:c>
       <x:c r="D11" s="360" t="n">
         <x:v>0</x:v>
@@ -4144,17 +6026,19 @@
       <x:c r="O11" s="361" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P11" s="306" t="n">
+      <x:c r="P11" s="306">
+        <x:f>Q11*1000</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="Q11" s="306" t="n">
+      <x:c r="Q11" s="306">
+        <x:f>Inertial_Properties!D10</x:f>
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="R11" s="301" t="str">
         <x:v>CAD physical-property report</x:v>
       </x:c>
       <x:c r="S11" s="301" t="str">
-        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_hip_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="T11" s="301" t="str">
         <x:v>CoM available</x:v>
@@ -4186,10 +6070,10 @@
         <x:v>rf_upper_leg_link</x:v>
       </x:c>
       <x:c r="B12" s="362" t="str">
-        <x:v>meshes/rf_upper_leg_link.stl</x:v>
+        <x:v>meshes/collision/rf_upper_leg_link.stl</x:v>
       </x:c>
       <x:c r="C12" s="362" t="str">
-        <x:v>meshes/rf_upper_leg_link.stl</x:v>
+        <x:v>meshes/collision/rf_upper_leg_link.stl</x:v>
       </x:c>
       <x:c r="D12" s="363" t="n">
         <x:v>0</x:v>
@@ -4227,17 +6111,19 @@
       <x:c r="O12" s="364" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P12" s="306" t="n">
-        <x:v>172.5</x:v>
-      </x:c>
-      <x:c r="Q12" s="306" t="n">
-        <x:v>0.1725</x:v>
+      <x:c r="P12" s="306">
+        <x:f>Q12*1000</x:f>
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="Q12" s="306">
+        <x:f>Inertial_Properties!D11</x:f>
+        <x:v>0.152</x:v>
       </x:c>
       <x:c r="R12" s="301" t="str">
         <x:v>CAD physical-property report</x:v>
       </x:c>
       <x:c r="S12" s="301" t="str">
-        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_upper_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="T12" s="301" t="str">
         <x:v>CoM available</x:v>
@@ -4269,10 +6155,10 @@
         <x:v>rf_lower_leg_link</x:v>
       </x:c>
       <x:c r="B13" s="359" t="str">
-        <x:v>meshes/rf_lower_leg_link.stl</x:v>
+        <x:v>meshes/collision/rf_lower_leg_link.stl</x:v>
       </x:c>
       <x:c r="C13" s="359" t="str">
-        <x:v>meshes/rf_lower_leg_link.stl</x:v>
+        <x:v>meshes/collision/rf_lower_leg_link.stl</x:v>
       </x:c>
       <x:c r="D13" s="360" t="n">
         <x:v>0</x:v>
@@ -4310,17 +6196,19 @@
       <x:c r="O13" s="361" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P13" s="306" t="n">
-        <x:v>59.5</x:v>
-      </x:c>
-      <x:c r="Q13" s="306" t="n">
-        <x:v>0.0595</x:v>
+      <x:c r="P13" s="306">
+        <x:f>Q13*1000</x:f>
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="Q13" s="306">
+        <x:f>Inertial_Properties!D12</x:f>
+        <x:v>0.059</x:v>
       </x:c>
       <x:c r="R13" s="301" t="str">
         <x:v>CAD physical-property report</x:v>
       </x:c>
       <x:c r="S13" s="301" t="str">
-        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_lower_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="T13" s="301" t="str">
         <x:v>CoM available</x:v>
@@ -4352,10 +6240,10 @@
         <x:v>rf_foot_link</x:v>
       </x:c>
       <x:c r="B14" s="359" t="str">
-        <x:v>meshes/rf_foot_link.stl</x:v>
+        <x:v>meshes/collision/rf_foot_link.stl</x:v>
       </x:c>
       <x:c r="C14" s="359" t="str">
-        <x:v>meshes/rf_foot_link.stl</x:v>
+        <x:v>meshes/collision/rf_foot_link.stl</x:v>
       </x:c>
       <x:c r="D14" s="360" t="n">
         <x:v>0</x:v>
@@ -4393,17 +6281,19 @@
       <x:c r="O14" s="361" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P14" s="306" t="n">
-        <x:v>17.5</x:v>
-      </x:c>
-      <x:c r="Q14" s="306" t="n">
-        <x:v>0.0175</x:v>
+      <x:c r="P14" s="306">
+        <x:f>Q14*1000</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q14" s="306">
+        <x:f>Inertial_Properties!D13</x:f>
+        <x:v>0.014</x:v>
       </x:c>
       <x:c r="R14" s="301" t="str">
         <x:v>CAD physical-property report</x:v>
       </x:c>
       <x:c r="S14" s="301" t="str">
-        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_foot_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="T14" s="301" t="str">
         <x:v>CoM available</x:v>
@@ -4435,10 +6325,10 @@
         <x:v>rh_hip_link</x:v>
       </x:c>
       <x:c r="B15" s="359" t="str">
-        <x:v>meshes/rh_hip_link.stl</x:v>
+        <x:v>meshes/collision/rh_hip_link.stl</x:v>
       </x:c>
       <x:c r="C15" s="359" t="str">
-        <x:v>meshes/rh_hip_link.stl</x:v>
+        <x:v>meshes/collision/rh_hip_link.stl</x:v>
       </x:c>
       <x:c r="D15" s="360" t="n">
         <x:v>0</x:v>
@@ -4476,17 +6366,19 @@
       <x:c r="O15" s="361" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P15" s="306" t="n">
+      <x:c r="P15" s="306">
+        <x:f>Q15*1000</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="Q15" s="306" t="n">
+      <x:c r="Q15" s="306">
+        <x:f>Inertial_Properties!D14</x:f>
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="R15" s="301" t="str">
         <x:v>CAD physical-property report</x:v>
       </x:c>
       <x:c r="S15" s="301" t="str">
-        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_hip_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="T15" s="301" t="str">
         <x:v>CoM available</x:v>
@@ -4518,10 +6410,10 @@
         <x:v>rh_upper_leg_link</x:v>
       </x:c>
       <x:c r="B16" s="362" t="str">
-        <x:v>meshes/rh_upper_leg_link.stl</x:v>
+        <x:v>meshes/collision/rh_upper_leg_link.stl</x:v>
       </x:c>
       <x:c r="C16" s="362" t="str">
-        <x:v>meshes/rh_upper_leg_link.stl</x:v>
+        <x:v>meshes/collision/rh_upper_leg_link.stl</x:v>
       </x:c>
       <x:c r="D16" s="363" t="n">
         <x:v>0</x:v>
@@ -4559,17 +6451,19 @@
       <x:c r="O16" s="364" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P16" s="306" t="n">
-        <x:v>172.5</x:v>
-      </x:c>
-      <x:c r="Q16" s="306" t="n">
-        <x:v>0.1725</x:v>
+      <x:c r="P16" s="306">
+        <x:f>Q16*1000</x:f>
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="Q16" s="306">
+        <x:f>Inertial_Properties!D15</x:f>
+        <x:v>0.152</x:v>
       </x:c>
       <x:c r="R16" s="301" t="str">
         <x:v>CAD physical-property report</x:v>
       </x:c>
       <x:c r="S16" s="301" t="str">
-        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_upper_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="T16" s="301" t="str">
         <x:v>CoM available</x:v>
@@ -4601,10 +6495,10 @@
         <x:v>rh_lower_leg_link</x:v>
       </x:c>
       <x:c r="B17" s="359" t="str">
-        <x:v>meshes/rh_lower_leg_link.stl</x:v>
+        <x:v>meshes/collision/rh_lower_leg_link.stl</x:v>
       </x:c>
       <x:c r="C17" s="359" t="str">
-        <x:v>meshes/rh_lower_leg_link.stl</x:v>
+        <x:v>meshes/collision/rh_lower_leg_link.stl</x:v>
       </x:c>
       <x:c r="D17" s="360" t="n">
         <x:v>0</x:v>
@@ -4642,17 +6536,19 @@
       <x:c r="O17" s="361" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P17" s="306" t="n">
-        <x:v>59.5</x:v>
-      </x:c>
-      <x:c r="Q17" s="306" t="n">
-        <x:v>0.0595</x:v>
+      <x:c r="P17" s="306">
+        <x:f>Q17*1000</x:f>
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="Q17" s="306">
+        <x:f>Inertial_Properties!D16</x:f>
+        <x:v>0.059</x:v>
       </x:c>
       <x:c r="R17" s="301" t="str">
         <x:v>CAD physical-property report</x:v>
       </x:c>
       <x:c r="S17" s="301" t="str">
-        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_lower_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="T17" s="301" t="str">
         <x:v>CoM available</x:v>
@@ -4684,10 +6580,10 @@
         <x:v>rh_foot_link</x:v>
       </x:c>
       <x:c r="B18" s="359" t="str">
-        <x:v>meshes/rh_foot_link.stl</x:v>
+        <x:v>meshes/collision/rh_foot_link.stl</x:v>
       </x:c>
       <x:c r="C18" s="359" t="str">
-        <x:v>meshes/rh_foot_link.stl</x:v>
+        <x:v>meshes/collision/rh_foot_link.stl</x:v>
       </x:c>
       <x:c r="D18" s="360" t="n">
         <x:v>0</x:v>
@@ -4725,17 +6621,19 @@
       <x:c r="O18" s="361" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P18" s="306" t="n">
-        <x:v>17.5</x:v>
-      </x:c>
-      <x:c r="Q18" s="306" t="n">
-        <x:v>0.0175</x:v>
+      <x:c r="P18" s="306">
+        <x:f>Q18*1000</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q18" s="306">
+        <x:f>Inertial_Properties!D17</x:f>
+        <x:v>0.014</x:v>
       </x:c>
       <x:c r="R18" s="301" t="str">
         <x:v>CAD physical-property report</x:v>
       </x:c>
       <x:c r="S18" s="301" t="str">
-        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_foot_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="T18" s="301" t="str">
         <x:v>CoM available</x:v>
@@ -4767,10 +6665,10 @@
         <x:v>lh_hip_link</x:v>
       </x:c>
       <x:c r="B19" s="359" t="str">
-        <x:v>meshes/lh_hip_link.stl</x:v>
+        <x:v>meshes/collision/lh_hip_link.stl</x:v>
       </x:c>
       <x:c r="C19" s="359" t="str">
-        <x:v>meshes/lh_hip_link.stl</x:v>
+        <x:v>meshes/collision/lh_hip_link.stl</x:v>
       </x:c>
       <x:c r="D19" s="360" t="n">
         <x:v>0</x:v>
@@ -4808,17 +6706,19 @@
       <x:c r="O19" s="361" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P19" s="306" t="n">
+      <x:c r="P19" s="306">
+        <x:f>Q19*1000</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="Q19" s="306" t="n">
+      <x:c r="Q19" s="306">
+        <x:f>Inertial_Properties!D18</x:f>
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="R19" s="301" t="str">
         <x:v>CAD physical-property report</x:v>
       </x:c>
       <x:c r="S19" s="301" t="str">
-        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_hip_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="T19" s="301" t="str">
         <x:v>CoM available</x:v>
@@ -4850,10 +6750,10 @@
         <x:v>lh_upper_leg_link</x:v>
       </x:c>
       <x:c r="B20" s="362" t="str">
-        <x:v>meshes/lh_upper_leg_link.stl</x:v>
+        <x:v>meshes/collision/lh_upper_leg_link.stl</x:v>
       </x:c>
       <x:c r="C20" s="362" t="str">
-        <x:v>meshes/lh_upper_leg_link.stl</x:v>
+        <x:v>meshes/collision/lh_upper_leg_link.stl</x:v>
       </x:c>
       <x:c r="D20" s="363" t="n">
         <x:v>0</x:v>
@@ -4891,17 +6791,19 @@
       <x:c r="O20" s="364" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P20" s="306" t="n">
-        <x:v>172.5</x:v>
-      </x:c>
-      <x:c r="Q20" s="306" t="n">
-        <x:v>0.1725</x:v>
+      <x:c r="P20" s="306">
+        <x:f>Q20*1000</x:f>
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="Q20" s="306">
+        <x:f>Inertial_Properties!D19</x:f>
+        <x:v>0.152</x:v>
       </x:c>
       <x:c r="R20" s="301" t="str">
         <x:v>CAD physical-property report</x:v>
       </x:c>
       <x:c r="S20" s="301" t="str">
-        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_upper_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="T20" s="301" t="str">
         <x:v>CoM available</x:v>
@@ -4933,10 +6835,10 @@
         <x:v>lh_lower_leg_link</x:v>
       </x:c>
       <x:c r="B21" s="359" t="str">
-        <x:v>meshes/lh_lower_leg_link.stl</x:v>
+        <x:v>meshes/collision/lh_lower_leg_link.stl</x:v>
       </x:c>
       <x:c r="C21" s="359" t="str">
-        <x:v>meshes/lh_lower_leg_link.stl</x:v>
+        <x:v>meshes/collision/lh_lower_leg_link.stl</x:v>
       </x:c>
       <x:c r="D21" s="360" t="n">
         <x:v>0</x:v>
@@ -4974,17 +6876,19 @@
       <x:c r="O21" s="361" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P21" s="306" t="n">
-        <x:v>59.5</x:v>
-      </x:c>
-      <x:c r="Q21" s="306" t="n">
-        <x:v>0.0595</x:v>
+      <x:c r="P21" s="306">
+        <x:f>Q21*1000</x:f>
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="Q21" s="306">
+        <x:f>Inertial_Properties!D20</x:f>
+        <x:v>0.059</x:v>
       </x:c>
       <x:c r="R21" s="301" t="str">
         <x:v>CAD physical-property report</x:v>
       </x:c>
       <x:c r="S21" s="301" t="str">
-        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_lower_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="T21" s="301" t="str">
         <x:v>CoM available</x:v>
@@ -5016,10 +6920,10 @@
         <x:v>lh_foot_link</x:v>
       </x:c>
       <x:c r="B22" s="359" t="str">
-        <x:v>meshes/lh_foot_link.stl</x:v>
+        <x:v>meshes/collision/lh_foot_link.stl</x:v>
       </x:c>
       <x:c r="C22" s="359" t="str">
-        <x:v>meshes/lh_foot_link.stl</x:v>
+        <x:v>meshes/collision/lh_foot_link.stl</x:v>
       </x:c>
       <x:c r="D22" s="360" t="n">
         <x:v>0</x:v>
@@ -5057,17 +6961,19 @@
       <x:c r="O22" s="361" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P22" s="306" t="n">
-        <x:v>17.5</x:v>
-      </x:c>
-      <x:c r="Q22" s="306" t="n">
-        <x:v>0.0175</x:v>
+      <x:c r="P22" s="306">
+        <x:f>Q22*1000</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q22" s="306">
+        <x:f>Inertial_Properties!D21</x:f>
+        <x:v>0.014</x:v>
       </x:c>
       <x:c r="R22" s="301" t="str">
         <x:v>CAD physical-property report</x:v>
       </x:c>
       <x:c r="S22" s="301" t="str">
-        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_foot_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="T22" s="301" t="str">
         <x:v>CoM available</x:v>
@@ -5175,7 +7081,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>MATDOG — Riferimento cinematica REV00</x:v>
+        <x:v>MATDOG — Riferimento cinematica REV01-FIX (modello matt_robodog_rev00)</x:v>
       </x:c>
       <x:c r="B1" s="5"/>
       <x:c r="C1" s="5"/>
@@ -5287,7 +7193,7 @@
         <x:v>Collisione attuale</x:v>
       </x:c>
       <x:c r="C12" s="115" t="str">
-        <x:v>Stessa mesh STL della visuale: valida per verifica geometrica; non ancora ottimizzata per fisica.</x:v>
+        <x:v>Visual e collision usano la stessa STL per link (meshes/collision/&lt;link&gt;.stl): valida per verifica geometrica; non ancora ottimizzata per fisica.</x:v>
       </x:c>
       <x:c r="D12" s="115"/>
       <x:c r="E12" s="115"/>
@@ -5432,7 +7338,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="382" t="str">
-        <x:v>Proprietà dinamiche REV00</x:v>
+        <x:v>Proprietà dinamiche REV01-FIX (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="B22" s="382"/>
       <x:c r="C22" s="382"/>
@@ -5445,7 +7351,7 @@
         <x:v>Masse per link</x:v>
       </x:c>
       <x:c r="C23" s="383" t="str">
-        <x:v>Masse CAD riconciliate: totale 17-link = 2.480 kg. Vedi Mass_Reconciliation.</x:v>
+        <x:v>Masse per-link dai report Solid Edge 2026-10-30: totale 17-link = 2.928 kg (assieme 2.937 kg, residuo 9 g = risoluzione 1 g). Vedi Mass_Reconciliation.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="34" customHeight="1">
@@ -5467,7 +7373,7 @@
         <x:v>Inerzia</x:v>
       </x:c>
       <x:c r="C25" s="301" t="str">
-        <x:v>Tensori al CoM ricostruiti da assi principali + raggi di girazione CAD e inseriti come blocchi &lt;inertial&gt;.</x:v>
+        <x:v>Tensori al CoM ricostruiti da assi principali + raggi di girazione CAD e inseriti come blocchi &lt;inertial&gt; (configurazione nominale con Jetson Orin).</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
@@ -5478,7 +7384,7 @@
         <x:v>Validazione</x:v>
       </x:c>
       <x:c r="C26" s="301" t="str">
-        <x:v>Somma 17 link: massa uguale all’assieme CAD; errore massimo CoM 0.374 mm rispetto al report assembly.</x:v>
+        <x:v>Somma 17 link vs assieme CAD: scarto massimo CoM 0.42 mm; momenti principali entro 1 %.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="34" customHeight="1">
@@ -5489,7 +7395,7 @@
         <x:v>Neck yaw actuator</x:v>
       </x:c>
       <x:c r="C27" s="301" t="str">
-        <x:v>Nessun link separato in REV00: non è stato aggiunto senza un report CAD della sua posa montata.</x:v>
+        <x:v>Nessun link separato: non è stato aggiunto senza un report CAD della sua posa montata.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5548,7 +7454,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="294" t="str">
-        <x:v>Masse, CoM e inerzie dinamiche sono ora definite dal CAD. Il foglio Inertial_Properties è la sorgente canonica dei valori URDF; Engineering_Weight_Source resta un confronto storico.</x:v>
+        <x:v>Masse, CoM e inerzie dinamiche sono definite dai report Solid Edge del 2026-10-30. Il foglio Inertial_Properties è la sorgente canonica dei valori URDF (le masse qui sono formule verso di esso); Engineering_Weight_Source resta un confronto storico.</x:v>
       </x:c>
       <x:c r="B2" s="294"/>
       <x:c r="C2" s="294"/>
@@ -5604,13 +7510,15 @@
         <x:v>Body</x:v>
       </x:c>
       <x:c r="C5" s="328" t="str">
-        <x:v>meshes/base_link.stl</x:v>
-      </x:c>
-      <x:c r="D5" s="329" t="n">
-        <x:v>1282</x:v>
-      </x:c>
-      <x:c r="E5" s="329" t="n">
-        <x:v>1.282</x:v>
+        <x:v>meshes/collision/base_link.stl</x:v>
+      </x:c>
+      <x:c r="D5" s="329">
+        <x:f>E5*1000</x:f>
+        <x:v>1828</x:v>
+      </x:c>
+      <x:c r="E5" s="329">
+        <x:f>Inertial_Properties!D5</x:f>
+        <x:v>1.828</x:v>
       </x:c>
       <x:c r="F5" s="328" t="str">
         <x:v>CAD physical-property subassembly</x:v>
@@ -5619,7 +7527,7 @@
         <x:v>Mass reconciliation + Solid Edge report</x:v>
       </x:c>
       <x:c r="H5" s="328" t="str">
-        <x:v>physprop__base_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>base_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="I5" s="328" t="str">
         <x:v>Direct CAD</x:v>
@@ -5639,12 +7547,14 @@
         <x:v>LF</x:v>
       </x:c>
       <x:c r="C6" s="331" t="str">
-        <x:v>meshes/lf_hip_link.stl</x:v>
-      </x:c>
-      <x:c r="D6" s="332" t="n">
+        <x:v>meshes/collision/lf_hip_link.stl</x:v>
+      </x:c>
+      <x:c r="D6" s="332">
+        <x:f>E6*1000</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E6" s="332" t="n">
+      <x:c r="E6" s="332">
+        <x:f>Inertial_Properties!D6</x:f>
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="F6" s="331" t="str">
@@ -5654,7 +7564,7 @@
         <x:v>Mass reconciliation + Solid Edge report</x:v>
       </x:c>
       <x:c r="H6" s="331" t="str">
-        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_hip_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="I6" s="331" t="str">
         <x:v>Direct CAD</x:v>
@@ -5674,13 +7584,15 @@
         <x:v>LF</x:v>
       </x:c>
       <x:c r="C7" s="334" t="str">
-        <x:v>meshes/lf_upper_leg_link.stl</x:v>
-      </x:c>
-      <x:c r="D7" s="335" t="n">
-        <x:v>172.5</x:v>
-      </x:c>
-      <x:c r="E7" s="335" t="n">
-        <x:v>0.1725</x:v>
+        <x:v>meshes/collision/lf_upper_leg_link.stl</x:v>
+      </x:c>
+      <x:c r="D7" s="335">
+        <x:f>E7*1000</x:f>
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="E7" s="335">
+        <x:f>Inertial_Properties!D7</x:f>
+        <x:v>0.152</x:v>
       </x:c>
       <x:c r="F7" s="334" t="str">
         <x:v>CAD physical-property subassembly</x:v>
@@ -5689,7 +7601,7 @@
         <x:v>Mass reconciliation + Solid Edge report</x:v>
       </x:c>
       <x:c r="H7" s="334" t="str">
-        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_upper_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="I7" s="334" t="str">
         <x:v>Direct CAD</x:v>
@@ -5709,13 +7621,15 @@
         <x:v>LF</x:v>
       </x:c>
       <x:c r="C8" s="337" t="str">
-        <x:v>meshes/lf_lower_leg_link.stl</x:v>
-      </x:c>
-      <x:c r="D8" s="338" t="n">
-        <x:v>59.5</x:v>
-      </x:c>
-      <x:c r="E8" s="338" t="n">
-        <x:v>0.0595</x:v>
+        <x:v>meshes/collision/lf_lower_leg_link.stl</x:v>
+      </x:c>
+      <x:c r="D8" s="338">
+        <x:f>E8*1000</x:f>
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E8" s="338">
+        <x:f>Inertial_Properties!D8</x:f>
+        <x:v>0.059</x:v>
       </x:c>
       <x:c r="F8" s="337" t="str">
         <x:v>CAD physical-property subassembly</x:v>
@@ -5724,7 +7638,7 @@
         <x:v>Mass reconciliation + Solid Edge report</x:v>
       </x:c>
       <x:c r="H8" s="337" t="str">
-        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_lower_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="I8" s="337" t="str">
         <x:v>Direct CAD</x:v>
@@ -5744,13 +7658,15 @@
         <x:v>LF</x:v>
       </x:c>
       <x:c r="C9" s="340" t="str">
-        <x:v>meshes/lf_foot_link.stl</x:v>
-      </x:c>
-      <x:c r="D9" s="341" t="n">
-        <x:v>17.5</x:v>
-      </x:c>
-      <x:c r="E9" s="341" t="n">
-        <x:v>0.0175</x:v>
+        <x:v>meshes/collision/lf_foot_link.stl</x:v>
+      </x:c>
+      <x:c r="D9" s="341">
+        <x:f>E9*1000</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E9" s="341">
+        <x:f>Inertial_Properties!D9</x:f>
+        <x:v>0.014</x:v>
       </x:c>
       <x:c r="F9" s="340" t="str">
         <x:v>CAD physical-property subassembly</x:v>
@@ -5759,7 +7675,7 @@
         <x:v>Mass reconciliation + Solid Edge report</x:v>
       </x:c>
       <x:c r="H9" s="340" t="str">
-        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_foot_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="I9" s="340" t="str">
         <x:v>Direct CAD</x:v>
@@ -5779,12 +7695,14 @@
         <x:v>RF</x:v>
       </x:c>
       <x:c r="C10" s="331" t="str">
-        <x:v>meshes/rf_hip_link.stl</x:v>
-      </x:c>
-      <x:c r="D10" s="332" t="n">
+        <x:v>meshes/collision/rf_hip_link.stl</x:v>
+      </x:c>
+      <x:c r="D10" s="332">
+        <x:f>E10*1000</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E10" s="332" t="n">
+      <x:c r="E10" s="332">
+        <x:f>Inertial_Properties!D10</x:f>
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="F10" s="331" t="str">
@@ -5794,7 +7712,7 @@
         <x:v>Mass reconciliation + Solid Edge report</x:v>
       </x:c>
       <x:c r="H10" s="331" t="str">
-        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_hip_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="I10" s="331" t="str">
         <x:v>LF symmetry-derived</x:v>
@@ -5814,13 +7732,15 @@
         <x:v>RF</x:v>
       </x:c>
       <x:c r="C11" s="334" t="str">
-        <x:v>meshes/rf_upper_leg_link.stl</x:v>
-      </x:c>
-      <x:c r="D11" s="335" t="n">
-        <x:v>172.5</x:v>
-      </x:c>
-      <x:c r="E11" s="335" t="n">
-        <x:v>0.1725</x:v>
+        <x:v>meshes/collision/rf_upper_leg_link.stl</x:v>
+      </x:c>
+      <x:c r="D11" s="335">
+        <x:f>E11*1000</x:f>
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="E11" s="335">
+        <x:f>Inertial_Properties!D11</x:f>
+        <x:v>0.152</x:v>
       </x:c>
       <x:c r="F11" s="334" t="str">
         <x:v>CAD physical-property subassembly</x:v>
@@ -5829,7 +7749,7 @@
         <x:v>Mass reconciliation + Solid Edge report</x:v>
       </x:c>
       <x:c r="H11" s="334" t="str">
-        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_upper_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="I11" s="334" t="str">
         <x:v>LF symmetry-derived</x:v>
@@ -5849,13 +7769,15 @@
         <x:v>RF</x:v>
       </x:c>
       <x:c r="C12" s="337" t="str">
-        <x:v>meshes/rf_lower_leg_link.stl</x:v>
-      </x:c>
-      <x:c r="D12" s="338" t="n">
-        <x:v>59.5</x:v>
-      </x:c>
-      <x:c r="E12" s="338" t="n">
-        <x:v>0.0595</x:v>
+        <x:v>meshes/collision/rf_lower_leg_link.stl</x:v>
+      </x:c>
+      <x:c r="D12" s="338">
+        <x:f>E12*1000</x:f>
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E12" s="338">
+        <x:f>Inertial_Properties!D12</x:f>
+        <x:v>0.059</x:v>
       </x:c>
       <x:c r="F12" s="337" t="str">
         <x:v>CAD physical-property subassembly</x:v>
@@ -5864,7 +7786,7 @@
         <x:v>Mass reconciliation + Solid Edge report</x:v>
       </x:c>
       <x:c r="H12" s="337" t="str">
-        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_lower_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="I12" s="337" t="str">
         <x:v>LF symmetry-derived</x:v>
@@ -5884,13 +7806,15 @@
         <x:v>RF</x:v>
       </x:c>
       <x:c r="C13" s="340" t="str">
-        <x:v>meshes/rf_foot_link.stl</x:v>
-      </x:c>
-      <x:c r="D13" s="341" t="n">
-        <x:v>17.5</x:v>
-      </x:c>
-      <x:c r="E13" s="341" t="n">
-        <x:v>0.0175</x:v>
+        <x:v>meshes/collision/rf_foot_link.stl</x:v>
+      </x:c>
+      <x:c r="D13" s="341">
+        <x:f>E13*1000</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E13" s="341">
+        <x:f>Inertial_Properties!D13</x:f>
+        <x:v>0.014</x:v>
       </x:c>
       <x:c r="F13" s="340" t="str">
         <x:v>CAD physical-property subassembly</x:v>
@@ -5899,7 +7823,7 @@
         <x:v>Mass reconciliation + Solid Edge report</x:v>
       </x:c>
       <x:c r="H13" s="340" t="str">
-        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_foot_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="I13" s="340" t="str">
         <x:v>LF symmetry-derived</x:v>
@@ -5919,12 +7843,14 @@
         <x:v>RH</x:v>
       </x:c>
       <x:c r="C14" s="331" t="str">
-        <x:v>meshes/rh_hip_link.stl</x:v>
-      </x:c>
-      <x:c r="D14" s="332" t="n">
+        <x:v>meshes/collision/rh_hip_link.stl</x:v>
+      </x:c>
+      <x:c r="D14" s="332">
+        <x:f>E14*1000</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E14" s="332" t="n">
+      <x:c r="E14" s="332">
+        <x:f>Inertial_Properties!D14</x:f>
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="F14" s="331" t="str">
@@ -5934,7 +7860,7 @@
         <x:v>Mass reconciliation + Solid Edge report</x:v>
       </x:c>
       <x:c r="H14" s="331" t="str">
-        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_hip_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="I14" s="331" t="str">
         <x:v>LF symmetry-derived</x:v>
@@ -5954,13 +7880,15 @@
         <x:v>RH</x:v>
       </x:c>
       <x:c r="C15" s="334" t="str">
-        <x:v>meshes/rh_upper_leg_link.stl</x:v>
-      </x:c>
-      <x:c r="D15" s="335" t="n">
-        <x:v>172.5</x:v>
-      </x:c>
-      <x:c r="E15" s="335" t="n">
-        <x:v>0.1725</x:v>
+        <x:v>meshes/collision/rh_upper_leg_link.stl</x:v>
+      </x:c>
+      <x:c r="D15" s="335">
+        <x:f>E15*1000</x:f>
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="E15" s="335">
+        <x:f>Inertial_Properties!D15</x:f>
+        <x:v>0.152</x:v>
       </x:c>
       <x:c r="F15" s="334" t="str">
         <x:v>CAD physical-property subassembly</x:v>
@@ -5969,7 +7897,7 @@
         <x:v>Mass reconciliation + Solid Edge report</x:v>
       </x:c>
       <x:c r="H15" s="334" t="str">
-        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_upper_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="I15" s="334" t="str">
         <x:v>LF symmetry-derived</x:v>
@@ -5989,13 +7917,15 @@
         <x:v>RH</x:v>
       </x:c>
       <x:c r="C16" s="337" t="str">
-        <x:v>meshes/rh_lower_leg_link.stl</x:v>
-      </x:c>
-      <x:c r="D16" s="338" t="n">
-        <x:v>59.5</x:v>
-      </x:c>
-      <x:c r="E16" s="338" t="n">
-        <x:v>0.0595</x:v>
+        <x:v>meshes/collision/rh_lower_leg_link.stl</x:v>
+      </x:c>
+      <x:c r="D16" s="338">
+        <x:f>E16*1000</x:f>
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E16" s="338">
+        <x:f>Inertial_Properties!D16</x:f>
+        <x:v>0.059</x:v>
       </x:c>
       <x:c r="F16" s="337" t="str">
         <x:v>CAD physical-property subassembly</x:v>
@@ -6004,7 +7934,7 @@
         <x:v>Mass reconciliation + Solid Edge report</x:v>
       </x:c>
       <x:c r="H16" s="337" t="str">
-        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_lower_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="I16" s="337" t="str">
         <x:v>LF symmetry-derived</x:v>
@@ -6024,13 +7954,15 @@
         <x:v>RH</x:v>
       </x:c>
       <x:c r="C17" s="340" t="str">
-        <x:v>meshes/rh_foot_link.stl</x:v>
-      </x:c>
-      <x:c r="D17" s="341" t="n">
-        <x:v>17.5</x:v>
-      </x:c>
-      <x:c r="E17" s="341" t="n">
-        <x:v>0.0175</x:v>
+        <x:v>meshes/collision/rh_foot_link.stl</x:v>
+      </x:c>
+      <x:c r="D17" s="341">
+        <x:f>E17*1000</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E17" s="341">
+        <x:f>Inertial_Properties!D17</x:f>
+        <x:v>0.014</x:v>
       </x:c>
       <x:c r="F17" s="340" t="str">
         <x:v>CAD physical-property subassembly</x:v>
@@ -6039,7 +7971,7 @@
         <x:v>Mass reconciliation + Solid Edge report</x:v>
       </x:c>
       <x:c r="H17" s="340" t="str">
-        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_foot_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="I17" s="340" t="str">
         <x:v>LF symmetry-derived</x:v>
@@ -6059,12 +7991,14 @@
         <x:v>LH</x:v>
       </x:c>
       <x:c r="C18" s="331" t="str">
-        <x:v>meshes/lh_hip_link.stl</x:v>
-      </x:c>
-      <x:c r="D18" s="332" t="n">
+        <x:v>meshes/collision/lh_hip_link.stl</x:v>
+      </x:c>
+      <x:c r="D18" s="332">
+        <x:f>E18*1000</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E18" s="332" t="n">
+      <x:c r="E18" s="332">
+        <x:f>Inertial_Properties!D18</x:f>
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="F18" s="331" t="str">
@@ -6074,7 +8008,7 @@
         <x:v>Mass reconciliation + Solid Edge report</x:v>
       </x:c>
       <x:c r="H18" s="331" t="str">
-        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_hip_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="I18" s="331" t="str">
         <x:v>LF symmetry-derived</x:v>
@@ -6094,13 +8028,15 @@
         <x:v>LH</x:v>
       </x:c>
       <x:c r="C19" s="334" t="str">
-        <x:v>meshes/lh_upper_leg_link.stl</x:v>
-      </x:c>
-      <x:c r="D19" s="335" t="n">
-        <x:v>172.5</x:v>
-      </x:c>
-      <x:c r="E19" s="335" t="n">
-        <x:v>0.1725</x:v>
+        <x:v>meshes/collision/lh_upper_leg_link.stl</x:v>
+      </x:c>
+      <x:c r="D19" s="335">
+        <x:f>E19*1000</x:f>
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="E19" s="335">
+        <x:f>Inertial_Properties!D19</x:f>
+        <x:v>0.152</x:v>
       </x:c>
       <x:c r="F19" s="334" t="str">
         <x:v>CAD physical-property subassembly</x:v>
@@ -6109,7 +8045,7 @@
         <x:v>Mass reconciliation + Solid Edge report</x:v>
       </x:c>
       <x:c r="H19" s="334" t="str">
-        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_upper_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="I19" s="334" t="str">
         <x:v>LF symmetry-derived</x:v>
@@ -6129,13 +8065,15 @@
         <x:v>LH</x:v>
       </x:c>
       <x:c r="C20" s="337" t="str">
-        <x:v>meshes/lh_lower_leg_link.stl</x:v>
-      </x:c>
-      <x:c r="D20" s="338" t="n">
-        <x:v>59.5</x:v>
-      </x:c>
-      <x:c r="E20" s="338" t="n">
-        <x:v>0.0595</x:v>
+        <x:v>meshes/collision/lh_lower_leg_link.stl</x:v>
+      </x:c>
+      <x:c r="D20" s="338">
+        <x:f>E20*1000</x:f>
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E20" s="338">
+        <x:f>Inertial_Properties!D20</x:f>
+        <x:v>0.059</x:v>
       </x:c>
       <x:c r="F20" s="337" t="str">
         <x:v>CAD physical-property subassembly</x:v>
@@ -6144,7 +8082,7 @@
         <x:v>Mass reconciliation + Solid Edge report</x:v>
       </x:c>
       <x:c r="H20" s="337" t="str">
-        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_lower_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="I20" s="337" t="str">
         <x:v>LF symmetry-derived</x:v>
@@ -6164,13 +8102,15 @@
         <x:v>LH</x:v>
       </x:c>
       <x:c r="C21" s="340" t="str">
-        <x:v>meshes/lh_foot_link.stl</x:v>
-      </x:c>
-      <x:c r="D21" s="341" t="n">
-        <x:v>17.5</x:v>
-      </x:c>
-      <x:c r="E21" s="341" t="n">
-        <x:v>0.0175</x:v>
+        <x:v>meshes/collision/lh_foot_link.stl</x:v>
+      </x:c>
+      <x:c r="D21" s="341">
+        <x:f>E21*1000</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E21" s="341">
+        <x:f>Inertial_Properties!D21</x:f>
+        <x:v>0.014</x:v>
       </x:c>
       <x:c r="F21" s="340" t="str">
         <x:v>CAD physical-property subassembly</x:v>
@@ -6179,7 +8119,7 @@
         <x:v>Mass reconciliation + Solid Edge report</x:v>
       </x:c>
       <x:c r="H21" s="340" t="str">
-        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_foot_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="I21" s="340" t="str">
         <x:v>LF symmetry-derived</x:v>
@@ -6217,7 +8157,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="289" t="str">
-        <x:v>MATDOG — Riepilogo masse REV00</x:v>
+        <x:v>MATDOG — Riepilogo masse REV01-FIX (CAD 2026-10-30)</x:v>
       </x:c>
       <x:c r="B1" s="289"/>
       <x:c r="C1" s="139"/>
@@ -6227,7 +8167,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="294" t="str">
-        <x:v>Baseline dinamica CAD: 17 link, 2.480 kg. Il dettaglio della riconciliazione tra CAD, calcolo pesi e misura fisica è nel foglio Mass_Reconciliation.</x:v>
+        <x:v>Un’unica configurazione nominale: 17 link con Jetson Orin (2.928 kg per-link; 2.937 kg assieme Solid Edge). La pesata reale del 2026-10-30 (2.807 kg, senza Jetson) è evidenza storica dell’hardware attualmente assemblato. Dettaglio in Mass_Reconciliation.</x:v>
       </x:c>
       <x:c r="B2" s="294"/>
       <x:c r="C2" s="144"/>
@@ -6247,56 +8187,63 @@
       <x:c r="A5" s="372" t="str">
         <x:v>URDF modeled links mass [g]</x:v>
       </x:c>
-      <x:c r="B5" s="306" t="n">
-        <x:v>2480</x:v>
+      <x:c r="B5" s="306">
+        <x:f>Inertial_Properties!D23*1000</x:f>
+        <x:v>2928</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="372" t="str">
         <x:v>URDF modeled links mass [kg]</x:v>
       </x:c>
-      <x:c r="B6" s="306" t="n">
-        <x:v>2.48</x:v>
+      <x:c r="B6" s="306">
+        <x:f>Inertial_Properties!D23</x:f>
+        <x:v>2.928</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="372" t="str">
         <x:v>Four legs mass [g]</x:v>
       </x:c>
-      <x:c r="B7" s="306" t="n">
-        <x:v>1198</x:v>
+      <x:c r="B7" s="306">
+        <x:f>SUM(Inertial_Properties!D6:D21)*1000</x:f>
+        <x:v>1100</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="372" t="str">
         <x:v>Base link mass [g]</x:v>
       </x:c>
-      <x:c r="B8" s="306" t="n">
-        <x:v>1282</x:v>
+      <x:c r="B8" s="306">
+        <x:f>Inertial_Properties!D5*1000</x:f>
+        <x:v>1828</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="372" t="str">
         <x:v>CAD full assembly [g]</x:v>
       </x:c>
-      <x:c r="B9" s="306" t="n">
-        <x:v>2480</x:v>
+      <x:c r="B9" s="306">
+        <x:f>CAD_Source_Data!D10*1000</x:f>
+        <x:v>2937</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="372" t="str">
-        <x:v>Weight-breakdown calculated [g]</x:v>
-      </x:c>
-      <x:c r="B10" s="306" t="n">
-        <x:v>2389.4</x:v>
+        <x:v>Weight-breakdown calculated, WITH Jetson [g]</x:v>
+      </x:c>
+      <x:c r="B10" s="306">
+        <x:f>'Weight_Evidence_2026-10-30'!J11+'Weight_Evidence_2026-10-30'!F16</x:f>
+        <x:v>2943.2</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="340" t="str">
-        <x:v>Physical robot measured [g]</x:v>
-      </x:c>
-      <x:c r="B11" s="341" t="n">
-        <x:v>2297</x:v>
+        <x:v>Physical robot measured 2026-10-30, WITHOUT Jetson [g]</x:v>
+      </x:c>
+      <x:c r="B11" s="341">
+        <x:f>'Weight_Evidence_2026-10-30'!J2</x:f>
+        <x:v>2807</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -6309,7 +8256,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="375" t="str">
-        <x:v>Standalone neck yaw link in REV00</x:v>
+        <x:v>Standalone neck yaw link in REV01-FIX</x:v>
       </x:c>
       <x:c r="B13" s="375" t="str">
         <x:v>No</x:v>
@@ -6324,12 +8271,65 @@
         <x:v>Dynamic property status</x:v>
       </x:c>
       <x:c r="B14" s="375" t="str">
-        <x:v>CAD CoM + inertia tensor inserted</x:v>
+        <x:v>CAD CoM + inertia tensor updated 2026-10-30 (REV01-FIX)</x:v>
       </x:c>
       <x:c r="C14" s="183"/>
       <x:c r="D14" s="183"/>
       <x:c r="E14" s="183"/>
       <x:c r="F14" s="184"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str" s="372">
+        <x:v>Jetson Orin, inside the base_link CAD [g]</x:v>
+      </x:c>
+      <x:c r="B15" s="306">
+        <x:f>'Weight_Evidence_2026-10-30'!F16</x:f>
+        <x:v>175</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str" s="372">
+        <x:v>CAD assembly WITHOUT Jetson [g]</x:v>
+      </x:c>
+      <x:c r="B16" s="306">
+        <x:f>B9-B15</x:f>
+        <x:v>2762</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str" s="372">
+        <x:v>Measured − (CAD assembly without Jetson) [g]</x:v>
+      </x:c>
+      <x:c r="B17" s="306">
+        <x:f>B11-B16</x:f>
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str" s="372">
+        <x:v>Weight workbook: measured − analytic without Jetson [g]</x:v>
+      </x:c>
+      <x:c r="B18" s="306">
+        <x:f>'Weight_Evidence_2026-10-30'!J13</x:f>
+        <x:v>38.80000000000018</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str" s="372">
+        <x:v>Model links − CAD assembly [g]</x:v>
+      </x:c>
+      <x:c r="B19" s="306">
+        <x:f>B5-B9</x:f>
+        <x:v>-9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str" s="372">
+        <x:v>Interpretation</x:v>
+      </x:c>
+      <x:c r="B20" t="str" s="372">
+        <x:v>Residual 38.8 g (workbook) / 45 g (vs CAD): unmodeled internal wiring is a HYPOTHESIS, not a measurement; no mass is added to the model.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -7679,7 +9679,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="289" t="str">
-        <x:v>MATDOG — Audit URDF REV00 con proprietà dinamiche</x:v>
+        <x:v>MATDOG — Audit URDF REV01-FIX con proprietà dinamiche</x:v>
       </x:c>
       <x:c r="B1" s="289"/>
       <x:c r="C1" s="289"/>
@@ -7805,10 +9805,10 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C10" s="301" t="str">
-        <x:v>34 riferimenti mesh (visual + collision), tutti relativi a meshes/*.stl; 17 asset unici; ogni mesh dichiara scale="0.001 0.001 0.001".</x:v>
+        <x:v>34 riferimenti mesh (visual + collision), tutti a meshes/collision/*.stl: una sola STL per link per entrambi; 17 asset unici; ogni mesh dichiara scale="0.001 0.001 0.001".</x:v>
       </x:c>
       <x:c r="D10" s="301" t="str">
-        <x:v>Scala URDF dichiarata per STL CAD in mm.</x:v>
+        <x:v>Unificati in REV01-FIX (STL solo estetiche rimosse).</x:v>
       </x:c>
       <x:c r="E10" s="301" t="str">
         <x:v>Canonico</x:v>
@@ -7856,7 +9856,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C13" s="391" t="str">
-        <x:v>2.480 kg from CAD reconciliation; every modeled link has a CAD CoM in its local URDF frame.</x:v>
+        <x:v>2.928 kg from the Solid Edge per-link reports of 2026-10-30 (assembly 2.937 kg; 9 g = 1 g report resolution); every modeled link has a CAD CoM in its local URDF frame.</x:v>
       </x:c>
       <x:c r="D13" s="391" t="str">
         <x:v>Inserted in standard &lt;inertial&gt; blocks.</x:v>
@@ -7873,7 +9873,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="C14" s="391" t="str">
-        <x:v>Tensors reconstructed at CoM from principal axes + radii of gyration; symmetry-derived legs aggregate-check against full CAD assembly.</x:v>
+        <x:v>Tensors reconstructed at CoM from principal axes + radii of gyration; positive definite, symmetric, triangle inequality verified; symmetry-derived legs aggregate-check against the full CAD assembly (CoM 0.42 mm).</x:v>
       </x:c>
       <x:c r="D14" s="391" t="str">
         <x:v>Inserted in standard &lt;inertial&gt; blocks.</x:v>
@@ -7890,13 +9890,30 @@
         <x:v>INFO</x:v>
       </x:c>
       <x:c r="C15" s="392" t="str">
-        <x:v>No standalone neck yaw link or mounted-frame inertial report is included in REV00.</x:v>
+        <x:v>No standalone neck yaw link or mounted-frame inertial report is included.</x:v>
       </x:c>
       <x:c r="D15" s="392" t="str">
         <x:v>Keep excluded until dedicated CAD export is available.</x:v>
       </x:c>
       <x:c r="E15" s="392" t="str">
         <x:v>Controlled scope</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str" s="392">
+        <x:v>Hip origin Z</x:v>
+      </x:c>
+      <x:c r="B16" t="str" s="392">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C16" t="str" s="392">
+        <x:v>LF/RF 0.0487 m, RH/LH 0.0287 m (+2.2 mm vs REV00); X/Y unchanged.</x:v>
+      </x:c>
+      <x:c r="D16" t="str" s="392">
+        <x:v>Aggiornato in REV01-FIX.</x:v>
+      </x:c>
+      <x:c r="E16" t="str" s="392">
+        <x:v>Canonico</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7943,7 +9960,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="289" t="str">
-        <x:v>MATDOG — Proprietà inerziali REV00</x:v>
+        <x:v>MATDOG — Proprietà inerziali REV01-FIX (Solid Edge 2026-10-30, configurazione nominale con Jetson Orin)</x:v>
       </x:c>
       <x:c r="B1" s="289"/>
       <x:c r="C1" s="289"/>
@@ -7964,7 +9981,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="294" t="str">
-        <x:v>Fonte canonica per il modello dinamico: masse CAD riconciliate, baricentri per-link e tensori d’inerzia al centro di massa, espressi nei frame URDF dei link.</x:v>
+        <x:v>Fonte canonica per il modello dinamico: masse dei report Solid Edge (risoluzione 1 g), baricentri per-link e tensori d’inerzia al centro di massa, espressi nei frame URDF dei link. Un’unica configurazione nominale, comprensiva della Jetson Orin (175 g, nel base_link). Lo storico REV00 è in Git (commit 0f8f7ff).</x:v>
       </x:c>
       <x:c r="B2" s="294"/>
       <x:c r="C2" s="294"/>
@@ -8056,35 +10073,35 @@
       <x:c r="C5" s="301" t="str">
         <x:v>Base assembly</x:v>
       </x:c>
-      <x:c r="D5" s="303" t="n">
-        <x:v>1.282</x:v>
-      </x:c>
-      <x:c r="E5" s="303" t="n">
-        <x:v>0.00584</x:v>
-      </x:c>
-      <x:c r="F5" s="303" t="n">
-        <x:v>-0.00065</x:v>
-      </x:c>
-      <x:c r="G5" s="303" t="n">
-        <x:v>0.02773</x:v>
-      </x:c>
-      <x:c r="H5" s="302" t="n">
-        <x:v>0.00147265728657</x:v>
-      </x:c>
-      <x:c r="I5" s="302" t="n">
-        <x:v>0.0000142294028465</x:v>
-      </x:c>
-      <x:c r="J5" s="302" t="n">
-        <x:v>-0.000443609672652</x:v>
-      </x:c>
-      <x:c r="K5" s="302" t="n">
-        <x:v>0.00887012995059</x:v>
-      </x:c>
-      <x:c r="L5" s="302" t="n">
-        <x:v>-0.00000770141299896</x:v>
-      </x:c>
-      <x:c r="M5" s="302" t="n">
-        <x:v>0.00949906085204</x:v>
+      <x:c r="D5" s="303">
+        <x:v>1.828</x:v>
+      </x:c>
+      <x:c r="E5" s="303">
+        <x:v>-0.00693</x:v>
+      </x:c>
+      <x:c r="F5" s="303">
+        <x:v>-0.00044</x:v>
+      </x:c>
+      <x:c r="G5" s="303">
+        <x:v>0.03657</x:v>
+      </x:c>
+      <x:c r="H5" s="302">
+        <x:v>0.0018854712506707848</x:v>
+      </x:c>
+      <x:c r="I5" s="302">
+        <x:v>-1.4261469087260915e-05</x:v>
+      </x:c>
+      <x:c r="J5" s="302">
+        <x:v>-0.0002559907740315669</x:v>
+      </x:c>
+      <x:c r="K5" s="302">
+        <x:v>0.013608332574946251</x:v>
+      </x:c>
+      <x:c r="L5" s="302">
+        <x:v>-1.159821782422323e-05</x:v>
+      </x:c>
+      <x:c r="M5" s="302">
+        <x:v>0.014054012486782997</x:v>
       </x:c>
       <x:c r="N5" s="301" t="str">
         <x:v>DIRECT CAD</x:v>
@@ -8093,10 +10110,10 @@
         <x:v>CAD direct: principal axes + radii of gyration</x:v>
       </x:c>
       <x:c r="P5" s="301" t="str">
-        <x:v>physprop__base_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>base_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="Q5" s="301" t="str">
-        <x:v>URDF &lt;inertial&gt; ready</x:v>
+        <x:v>URDF &lt;inertial&gt; updated 2026-10-31</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -8109,35 +10126,35 @@
       <x:c r="C6" s="301" t="str">
         <x:v>Hip subassembly</x:v>
       </x:c>
-      <x:c r="D6" s="303" t="n">
+      <x:c r="D6" s="303">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="E6" s="303" t="n">
+      <x:c r="E6" s="303">
         <x:v>0.00366</x:v>
       </x:c>
-      <x:c r="F6" s="303" t="n">
+      <x:c r="F6" s="303">
         <x:v>0.02982</x:v>
       </x:c>
-      <x:c r="G6" s="303" t="n">
+      <x:c r="G6" s="303">
         <x:v>0.00694</x:v>
       </x:c>
-      <x:c r="H6" s="302" t="n">
-        <x:v>0.0000402252347591</x:v>
-      </x:c>
-      <x:c r="I6" s="302" t="n">
-        <x:v>-0.00000131462768927</x:v>
-      </x:c>
-      <x:c r="J6" s="302" t="n">
-        <x:v>-0.00000113953716339</x:v>
-      </x:c>
-      <x:c r="K6" s="302" t="n">
-        <x:v>0.000018958128496</x:v>
-      </x:c>
-      <x:c r="L6" s="302" t="n">
-        <x:v>-0.00000446400670021</x:v>
-      </x:c>
-      <x:c r="M6" s="302" t="n">
-        <x:v>0.0000454280867449</x:v>
+      <x:c r="H6" s="302">
+        <x:v>4.022523475913449e-05</x:v>
+      </x:c>
+      <x:c r="I6" s="302">
+        <x:v>-1.3146276892716857e-06</x:v>
+      </x:c>
+      <x:c r="J6" s="302">
+        <x:v>-1.1395371633858386e-06</x:v>
+      </x:c>
+      <x:c r="K6" s="302">
+        <x:v>1.8958128496012147e-05</x:v>
+      </x:c>
+      <x:c r="L6" s="302">
+        <x:v>-4.464006700211402e-06</x:v>
+      </x:c>
+      <x:c r="M6" s="302">
+        <x:v>4.542808674485334e-05</x:v>
       </x:c>
       <x:c r="N6" s="301" t="str">
         <x:v>DIRECT CAD</x:v>
@@ -8146,10 +10163,10 @@
         <x:v>CAD direct: principal axes + radii of gyration</x:v>
       </x:c>
       <x:c r="P6" s="301" t="str">
-        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_hip_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="Q6" s="301" t="str">
-        <x:v>URDF &lt;inertial&gt; ready</x:v>
+        <x:v>URDF &lt;inertial&gt; updated 2026-10-31</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -8162,35 +10179,35 @@
       <x:c r="C7" s="301" t="str">
         <x:v>Upper-leg subassembly</x:v>
       </x:c>
-      <x:c r="D7" s="303" t="n">
-        <x:v>0.1725</x:v>
-      </x:c>
-      <x:c r="E7" s="303" t="n">
-        <x:v>0.00108</x:v>
-      </x:c>
-      <x:c r="F7" s="303" t="n">
-        <x:v>0.00015</x:v>
-      </x:c>
-      <x:c r="G7" s="303" t="n">
+      <x:c r="D7" s="303">
+        <x:v>0.152</x:v>
+      </x:c>
+      <x:c r="E7" s="303">
+        <x:v>0.00122</x:v>
+      </x:c>
+      <x:c r="F7" s="303">
+        <x:v>0.00014</x:v>
+      </x:c>
+      <x:c r="G7" s="303">
         <x:v>-0.04503</x:v>
       </x:c>
-      <x:c r="H7" s="302" t="n">
-        <x:v>0.000205436660094</x:v>
-      </x:c>
-      <x:c r="I7" s="302" t="n">
-        <x:v>-5.63507198417e-8</x:v>
-      </x:c>
-      <x:c r="J7" s="302" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K7" s="302" t="n">
-        <x:v>0.000199175976156</x:v>
-      </x:c>
-      <x:c r="L7" s="302" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M7" s="302" t="n">
-        <x:v>0.00003111294525</x:v>
+      <x:c r="H7" s="302">
+        <x:v>0.0001793475307052647</x:v>
+      </x:c>
+      <x:c r="I7" s="302">
+        <x:v>-6.26631577579123e-08</x:v>
+      </x:c>
+      <x:c r="J7" s="302">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7" s="302">
+        <x:v>0.0001736515692947353</x:v>
+      </x:c>
+      <x:c r="L7" s="302">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" s="302">
+        <x:v>2.8445644799999997e-05</x:v>
       </x:c>
       <x:c r="N7" s="301" t="str">
         <x:v>DIRECT CAD</x:v>
@@ -8199,10 +10216,10 @@
         <x:v>CAD direct: principal axes + radii of gyration</x:v>
       </x:c>
       <x:c r="P7" s="301" t="str">
-        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_upper_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="Q7" s="301" t="str">
-        <x:v>URDF &lt;inertial&gt; ready</x:v>
+        <x:v>URDF &lt;inertial&gt; updated 2026-10-31</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -8215,35 +10232,35 @@
       <x:c r="C8" s="301" t="str">
         <x:v>Lower-leg subassembly</x:v>
       </x:c>
-      <x:c r="D8" s="303" t="n">
-        <x:v>0.0595</x:v>
-      </x:c>
-      <x:c r="E8" s="303" t="n">
+      <x:c r="D8" s="303">
+        <x:v>0.059</x:v>
+      </x:c>
+      <x:c r="E8" s="303">
         <x:v>0.03075</x:v>
       </x:c>
-      <x:c r="F8" s="303" t="n">
+      <x:c r="F8" s="303">
         <x:v>-0.00118</x:v>
       </x:c>
-      <x:c r="G8" s="303" t="n">
+      <x:c r="G8" s="303">
         <x:v>-0.01958</x:v>
       </x:c>
-      <x:c r="H8" s="302" t="n">
-        <x:v>0.0000215172642767</x:v>
-      </x:c>
-      <x:c r="I8" s="302" t="n">
-        <x:v>6.0930015348e-7</x:v>
-      </x:c>
-      <x:c r="J8" s="302" t="n">
-        <x:v>0.0000168302311374</x:v>
-      </x:c>
-      <x:c r="K8" s="302" t="n">
-        <x:v>0.000102530052784</x:v>
-      </x:c>
-      <x:c r="L8" s="302" t="n">
-        <x:v>-3.71953235117e-7</x:v>
-      </x:c>
-      <x:c r="M8" s="302" t="n">
-        <x:v>0.000104321477439</x:v>
+      <x:c r="H8" s="302">
+        <x:v>2.1336446929790997e-05</x:v>
+      </x:c>
+      <x:c r="I8" s="302">
+        <x:v>6.041799841230725e-07</x:v>
+      </x:c>
+      <x:c r="J8" s="302">
+        <x:v>1.6688800623674613e-05</x:v>
+      </x:c>
+      <x:c r="K8" s="302">
+        <x:v>0.00010166845570177805</x:v>
+      </x:c>
+      <x:c r="L8" s="302">
+        <x:v>-3.688275776795085e-07</x:v>
+      </x:c>
+      <x:c r="M8" s="302">
+        <x:v>0.00010344482636843086</x:v>
       </x:c>
       <x:c r="N8" s="301" t="str">
         <x:v>DIRECT CAD</x:v>
@@ -8252,10 +10269,10 @@
         <x:v>CAD direct: principal axes + radii of gyration</x:v>
       </x:c>
       <x:c r="P8" s="301" t="str">
-        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_lower_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="Q8" s="301" t="str">
-        <x:v>URDF &lt;inertial&gt; ready</x:v>
+        <x:v>URDF &lt;inertial&gt; updated 2026-10-31</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -8268,35 +10285,35 @@
       <x:c r="C9" s="301" t="str">
         <x:v>Foot subassembly</x:v>
       </x:c>
-      <x:c r="D9" s="303" t="n">
-        <x:v>0.0175</x:v>
-      </x:c>
-      <x:c r="E9" s="303" t="n">
-        <x:v>-0.00052</x:v>
-      </x:c>
-      <x:c r="F9" s="303" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="303" t="n">
-        <x:v>0.01548</x:v>
-      </x:c>
-      <x:c r="H9" s="302" t="n">
-        <x:v>0.00000114526961866</x:v>
-      </x:c>
-      <x:c r="I9" s="302" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J9" s="302" t="n">
-        <x:v>-1.55064671079e-8</x:v>
-      </x:c>
-      <x:c r="K9" s="302" t="n">
-        <x:v>0.00000120267175</x:v>
-      </x:c>
-      <x:c r="L9" s="302" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M9" s="302" t="n">
-        <x:v>0.00000114835213134</x:v>
+      <x:c r="D9" s="303">
+        <x:v>0.014</x:v>
+      </x:c>
+      <x:c r="E9" s="303">
+        <x:v>-0.00074</x:v>
+      </x:c>
+      <x:c r="F9" s="303">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="303">
+        <x:v>0.01572</x:v>
+      </x:c>
+      <x:c r="H9" s="302">
+        <x:v>8.920990589937979e-07</x:v>
+      </x:c>
+      <x:c r="I9" s="302">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="302">
+        <x:v>-5.562092867964478e-09</x:v>
+      </x:c>
+      <x:c r="K9" s="302">
+        <x:v>8.430463999999999e-07</x:v>
+      </x:c>
+      <x:c r="L9" s="302">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" s="302">
+        <x:v>8.932047410062023e-07</x:v>
       </x:c>
       <x:c r="N9" s="301" t="str">
         <x:v>DIRECT CAD</x:v>
@@ -8305,10 +10322,10 @@
         <x:v>CAD direct: principal axes + radii of gyration</x:v>
       </x:c>
       <x:c r="P9" s="301" t="str">
-        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_foot_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="Q9" s="301" t="str">
-        <x:v>URDF &lt;inertial&gt; ready</x:v>
+        <x:v>URDF &lt;inertial&gt; updated 2026-10-31</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -8321,47 +10338,47 @@
       <x:c r="C10" s="301" t="str">
         <x:v>Hip subassembly</x:v>
       </x:c>
-      <x:c r="D10" s="303" t="n">
+      <x:c r="D10" s="303">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="E10" s="303" t="n">
+      <x:c r="E10" s="303">
         <x:v>0.00366</x:v>
       </x:c>
-      <x:c r="F10" s="303" t="n">
+      <x:c r="F10" s="303">
         <x:v>-0.02982</x:v>
       </x:c>
-      <x:c r="G10" s="303" t="n">
+      <x:c r="G10" s="303">
         <x:v>0.00694</x:v>
       </x:c>
-      <x:c r="H10" s="302" t="n">
-        <x:v>0.0000402252347591</x:v>
-      </x:c>
-      <x:c r="I10" s="302" t="n">
-        <x:v>0.00000131462768927</x:v>
-      </x:c>
-      <x:c r="J10" s="302" t="n">
-        <x:v>-0.00000113953716339</x:v>
-      </x:c>
-      <x:c r="K10" s="302" t="n">
-        <x:v>0.000018958128496</x:v>
-      </x:c>
-      <x:c r="L10" s="302" t="n">
-        <x:v>0.00000446400670021</x:v>
-      </x:c>
-      <x:c r="M10" s="302" t="n">
-        <x:v>0.0000454280867449</x:v>
+      <x:c r="H10" s="302">
+        <x:v>4.022523475913449e-05</x:v>
+      </x:c>
+      <x:c r="I10" s="302">
+        <x:v>1.3146276892716857e-06</x:v>
+      </x:c>
+      <x:c r="J10" s="302">
+        <x:v>-1.1395371633858386e-06</x:v>
+      </x:c>
+      <x:c r="K10" s="302">
+        <x:v>1.8958128496012147e-05</x:v>
+      </x:c>
+      <x:c r="L10" s="302">
+        <x:v>4.464006700211402e-06</x:v>
+      </x:c>
+      <x:c r="M10" s="302">
+        <x:v>4.542808674485334e-05</x:v>
       </x:c>
       <x:c r="N10" s="301" t="str">
         <x:v>DERIVED BY SYMMETRY</x:v>
       </x:c>
       <x:c r="O10" s="301" t="str">
-        <x:v>CAD symmetry-derived from LF: local Y reflection</x:v>
+        <x:v>CAD symmetry-derived from LF: Y reflection of LF</x:v>
       </x:c>
       <x:c r="P10" s="301" t="str">
-        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_hip_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="Q10" s="301" t="str">
-        <x:v>URDF &lt;inertial&gt; ready</x:v>
+        <x:v>URDF &lt;inertial&gt; updated 2026-10-31</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -8374,47 +10391,47 @@
       <x:c r="C11" s="301" t="str">
         <x:v>Upper-leg subassembly</x:v>
       </x:c>
-      <x:c r="D11" s="303" t="n">
-        <x:v>0.1725</x:v>
-      </x:c>
-      <x:c r="E11" s="303" t="n">
-        <x:v>0.00108</x:v>
-      </x:c>
-      <x:c r="F11" s="303" t="n">
-        <x:v>-0.00015</x:v>
-      </x:c>
-      <x:c r="G11" s="303" t="n">
+      <x:c r="D11" s="303">
+        <x:v>0.152</x:v>
+      </x:c>
+      <x:c r="E11" s="303">
+        <x:v>0.00122</x:v>
+      </x:c>
+      <x:c r="F11" s="303">
+        <x:v>-0.00014</x:v>
+      </x:c>
+      <x:c r="G11" s="303">
         <x:v>-0.04503</x:v>
       </x:c>
-      <x:c r="H11" s="302" t="n">
-        <x:v>0.000205436660094</x:v>
-      </x:c>
-      <x:c r="I11" s="302" t="n">
-        <x:v>5.63507198417e-8</x:v>
-      </x:c>
-      <x:c r="J11" s="302" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K11" s="302" t="n">
-        <x:v>0.000199175976156</x:v>
-      </x:c>
-      <x:c r="L11" s="302" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M11" s="302" t="n">
-        <x:v>0.00003111294525</x:v>
+      <x:c r="H11" s="302">
+        <x:v>0.0001793475307052647</x:v>
+      </x:c>
+      <x:c r="I11" s="302">
+        <x:v>6.26631577579123e-08</x:v>
+      </x:c>
+      <x:c r="J11" s="302">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K11" s="302">
+        <x:v>0.0001736515692947353</x:v>
+      </x:c>
+      <x:c r="L11" s="302">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" s="302">
+        <x:v>2.8445644799999997e-05</x:v>
       </x:c>
       <x:c r="N11" s="301" t="str">
         <x:v>DERIVED BY SYMMETRY</x:v>
       </x:c>
       <x:c r="O11" s="301" t="str">
-        <x:v>CAD symmetry-derived from LF: local Y reflection</x:v>
+        <x:v>CAD symmetry-derived from LF: Y reflection of LF</x:v>
       </x:c>
       <x:c r="P11" s="301" t="str">
-        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_upper_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="Q11" s="301" t="str">
-        <x:v>URDF &lt;inertial&gt; ready</x:v>
+        <x:v>URDF &lt;inertial&gt; updated 2026-10-31</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -8427,47 +10444,47 @@
       <x:c r="C12" s="301" t="str">
         <x:v>Lower-leg subassembly</x:v>
       </x:c>
-      <x:c r="D12" s="303" t="n">
-        <x:v>0.0595</x:v>
-      </x:c>
-      <x:c r="E12" s="303" t="n">
+      <x:c r="D12" s="303">
+        <x:v>0.059</x:v>
+      </x:c>
+      <x:c r="E12" s="303">
         <x:v>0.03075</x:v>
       </x:c>
-      <x:c r="F12" s="303" t="n">
+      <x:c r="F12" s="303">
         <x:v>0.00118</x:v>
       </x:c>
-      <x:c r="G12" s="303" t="n">
+      <x:c r="G12" s="303">
         <x:v>-0.01958</x:v>
       </x:c>
-      <x:c r="H12" s="302" t="n">
-        <x:v>0.0000215172642767</x:v>
-      </x:c>
-      <x:c r="I12" s="302" t="n">
-        <x:v>-6.0930015348e-7</x:v>
-      </x:c>
-      <x:c r="J12" s="302" t="n">
-        <x:v>0.0000168302311374</x:v>
-      </x:c>
-      <x:c r="K12" s="302" t="n">
-        <x:v>0.000102530052784</x:v>
-      </x:c>
-      <x:c r="L12" s="302" t="n">
-        <x:v>3.71953235117e-7</x:v>
-      </x:c>
-      <x:c r="M12" s="302" t="n">
-        <x:v>0.000104321477439</x:v>
+      <x:c r="H12" s="302">
+        <x:v>2.1336446929790997e-05</x:v>
+      </x:c>
+      <x:c r="I12" s="302">
+        <x:v>-6.041799841230725e-07</x:v>
+      </x:c>
+      <x:c r="J12" s="302">
+        <x:v>1.6688800623674613e-05</x:v>
+      </x:c>
+      <x:c r="K12" s="302">
+        <x:v>0.00010166845570177805</x:v>
+      </x:c>
+      <x:c r="L12" s="302">
+        <x:v>3.688275776795085e-07</x:v>
+      </x:c>
+      <x:c r="M12" s="302">
+        <x:v>0.00010344482636843086</x:v>
       </x:c>
       <x:c r="N12" s="301" t="str">
         <x:v>DERIVED BY SYMMETRY</x:v>
       </x:c>
       <x:c r="O12" s="301" t="str">
-        <x:v>CAD symmetry-derived from LF: local Y reflection</x:v>
+        <x:v>CAD symmetry-derived from LF: Y reflection of LF</x:v>
       </x:c>
       <x:c r="P12" s="301" t="str">
-        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_lower_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="Q12" s="301" t="str">
-        <x:v>URDF &lt;inertial&gt; ready</x:v>
+        <x:v>URDF &lt;inertial&gt; updated 2026-10-31</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -8480,47 +10497,47 @@
       <x:c r="C13" s="301" t="str">
         <x:v>Foot subassembly</x:v>
       </x:c>
-      <x:c r="D13" s="303" t="n">
-        <x:v>0.0175</x:v>
-      </x:c>
-      <x:c r="E13" s="303" t="n">
-        <x:v>-0.00052</x:v>
-      </x:c>
-      <x:c r="F13" s="303" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="303" t="n">
-        <x:v>0.01548</x:v>
-      </x:c>
-      <x:c r="H13" s="302" t="n">
-        <x:v>0.00000114526961866</x:v>
-      </x:c>
-      <x:c r="I13" s="302" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J13" s="302" t="n">
-        <x:v>-1.55064671079e-8</x:v>
-      </x:c>
-      <x:c r="K13" s="302" t="n">
-        <x:v>0.00000120267175</x:v>
-      </x:c>
-      <x:c r="L13" s="302" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M13" s="302" t="n">
-        <x:v>0.00000114835213134</x:v>
+      <x:c r="D13" s="303">
+        <x:v>0.014</x:v>
+      </x:c>
+      <x:c r="E13" s="303">
+        <x:v>-0.00074</x:v>
+      </x:c>
+      <x:c r="F13" s="303">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="303">
+        <x:v>0.01572</x:v>
+      </x:c>
+      <x:c r="H13" s="302">
+        <x:v>8.920990589937979e-07</x:v>
+      </x:c>
+      <x:c r="I13" s="302">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="302">
+        <x:v>-5.562092867964478e-09</x:v>
+      </x:c>
+      <x:c r="K13" s="302">
+        <x:v>8.430463999999999e-07</x:v>
+      </x:c>
+      <x:c r="L13" s="302">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="302">
+        <x:v>8.932047410062023e-07</x:v>
       </x:c>
       <x:c r="N13" s="301" t="str">
         <x:v>DERIVED BY SYMMETRY</x:v>
       </x:c>
       <x:c r="O13" s="301" t="str">
-        <x:v>CAD symmetry-derived from LF: identical foot geometry</x:v>
+        <x:v>CAD symmetry-derived from LF: identical foot geometry (LF copied)</x:v>
       </x:c>
       <x:c r="P13" s="301" t="str">
-        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_foot_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="Q13" s="301" t="str">
-        <x:v>URDF &lt;inertial&gt; ready</x:v>
+        <x:v>URDF &lt;inertial&gt; updated 2026-10-31</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -8533,47 +10550,47 @@
       <x:c r="C14" s="301" t="str">
         <x:v>Hip subassembly</x:v>
       </x:c>
-      <x:c r="D14" s="303" t="n">
+      <x:c r="D14" s="303">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="E14" s="303" t="n">
+      <x:c r="E14" s="303">
         <x:v>0.00366</x:v>
       </x:c>
-      <x:c r="F14" s="303" t="n">
+      <x:c r="F14" s="303">
         <x:v>-0.02982</x:v>
       </x:c>
-      <x:c r="G14" s="303" t="n">
+      <x:c r="G14" s="303">
         <x:v>0.00694</x:v>
       </x:c>
-      <x:c r="H14" s="302" t="n">
-        <x:v>0.0000402252347591</x:v>
-      </x:c>
-      <x:c r="I14" s="302" t="n">
-        <x:v>0.00000131462768927</x:v>
-      </x:c>
-      <x:c r="J14" s="302" t="n">
-        <x:v>-0.00000113953716339</x:v>
-      </x:c>
-      <x:c r="K14" s="302" t="n">
-        <x:v>0.000018958128496</x:v>
-      </x:c>
-      <x:c r="L14" s="302" t="n">
-        <x:v>0.00000446400670021</x:v>
-      </x:c>
-      <x:c r="M14" s="302" t="n">
-        <x:v>0.0000454280867449</x:v>
+      <x:c r="H14" s="302">
+        <x:v>4.022523475913449e-05</x:v>
+      </x:c>
+      <x:c r="I14" s="302">
+        <x:v>1.3146276892716857e-06</x:v>
+      </x:c>
+      <x:c r="J14" s="302">
+        <x:v>-1.1395371633858386e-06</x:v>
+      </x:c>
+      <x:c r="K14" s="302">
+        <x:v>1.8958128496012147e-05</x:v>
+      </x:c>
+      <x:c r="L14" s="302">
+        <x:v>4.464006700211402e-06</x:v>
+      </x:c>
+      <x:c r="M14" s="302">
+        <x:v>4.542808674485334e-05</x:v>
       </x:c>
       <x:c r="N14" s="301" t="str">
         <x:v>DERIVED BY SYMMETRY</x:v>
       </x:c>
       <x:c r="O14" s="301" t="str">
-        <x:v>CAD symmetry-derived from LF: local Y reflection</x:v>
+        <x:v>CAD symmetry-derived from LF: Y reflection of LF (rear hip mesh differs from LF by 0.21 mm CoM / 0.8 % inertia: mesh estimate, not CAD)</x:v>
       </x:c>
       <x:c r="P14" s="301" t="str">
-        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_hip_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="Q14" s="301" t="str">
-        <x:v>URDF &lt;inertial&gt; ready</x:v>
+        <x:v>URDF &lt;inertial&gt; updated 2026-10-31</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -8586,47 +10603,47 @@
       <x:c r="C15" s="301" t="str">
         <x:v>Upper-leg subassembly</x:v>
       </x:c>
-      <x:c r="D15" s="303" t="n">
-        <x:v>0.1725</x:v>
-      </x:c>
-      <x:c r="E15" s="303" t="n">
-        <x:v>0.00108</x:v>
-      </x:c>
-      <x:c r="F15" s="303" t="n">
-        <x:v>-0.00015</x:v>
-      </x:c>
-      <x:c r="G15" s="303" t="n">
+      <x:c r="D15" s="303">
+        <x:v>0.152</x:v>
+      </x:c>
+      <x:c r="E15" s="303">
+        <x:v>0.00122</x:v>
+      </x:c>
+      <x:c r="F15" s="303">
+        <x:v>-0.00014</x:v>
+      </x:c>
+      <x:c r="G15" s="303">
         <x:v>-0.04503</x:v>
       </x:c>
-      <x:c r="H15" s="302" t="n">
-        <x:v>0.000205436660094</x:v>
-      </x:c>
-      <x:c r="I15" s="302" t="n">
-        <x:v>5.63507198417e-8</x:v>
-      </x:c>
-      <x:c r="J15" s="302" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K15" s="302" t="n">
-        <x:v>0.000199175976156</x:v>
-      </x:c>
-      <x:c r="L15" s="302" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M15" s="302" t="n">
-        <x:v>0.00003111294525</x:v>
+      <x:c r="H15" s="302">
+        <x:v>0.0001793475307052647</x:v>
+      </x:c>
+      <x:c r="I15" s="302">
+        <x:v>6.26631577579123e-08</x:v>
+      </x:c>
+      <x:c r="J15" s="302">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="302">
+        <x:v>0.0001736515692947353</x:v>
+      </x:c>
+      <x:c r="L15" s="302">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="302">
+        <x:v>2.8445644799999997e-05</x:v>
       </x:c>
       <x:c r="N15" s="301" t="str">
         <x:v>DERIVED BY SYMMETRY</x:v>
       </x:c>
       <x:c r="O15" s="301" t="str">
-        <x:v>CAD symmetry-derived from LF: local Y reflection</x:v>
+        <x:v>CAD symmetry-derived from LF: Y reflection of LF</x:v>
       </x:c>
       <x:c r="P15" s="301" t="str">
-        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_upper_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="Q15" s="301" t="str">
-        <x:v>URDF &lt;inertial&gt; ready</x:v>
+        <x:v>URDF &lt;inertial&gt; updated 2026-10-31</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -8639,47 +10656,47 @@
       <x:c r="C16" s="301" t="str">
         <x:v>Lower-leg subassembly</x:v>
       </x:c>
-      <x:c r="D16" s="303" t="n">
-        <x:v>0.0595</x:v>
-      </x:c>
-      <x:c r="E16" s="303" t="n">
+      <x:c r="D16" s="303">
+        <x:v>0.059</x:v>
+      </x:c>
+      <x:c r="E16" s="303">
         <x:v>0.03075</x:v>
       </x:c>
-      <x:c r="F16" s="303" t="n">
+      <x:c r="F16" s="303">
         <x:v>0.00118</x:v>
       </x:c>
-      <x:c r="G16" s="303" t="n">
+      <x:c r="G16" s="303">
         <x:v>-0.01958</x:v>
       </x:c>
-      <x:c r="H16" s="302" t="n">
-        <x:v>0.0000215172642767</x:v>
-      </x:c>
-      <x:c r="I16" s="302" t="n">
-        <x:v>-6.0930015348e-7</x:v>
-      </x:c>
-      <x:c r="J16" s="302" t="n">
-        <x:v>0.0000168302311374</x:v>
-      </x:c>
-      <x:c r="K16" s="302" t="n">
-        <x:v>0.000102530052784</x:v>
-      </x:c>
-      <x:c r="L16" s="302" t="n">
-        <x:v>3.71953235117e-7</x:v>
-      </x:c>
-      <x:c r="M16" s="302" t="n">
-        <x:v>0.000104321477439</x:v>
+      <x:c r="H16" s="302">
+        <x:v>2.1336446929790997e-05</x:v>
+      </x:c>
+      <x:c r="I16" s="302">
+        <x:v>-6.041799841230725e-07</x:v>
+      </x:c>
+      <x:c r="J16" s="302">
+        <x:v>1.6688800623674613e-05</x:v>
+      </x:c>
+      <x:c r="K16" s="302">
+        <x:v>0.00010166845570177805</x:v>
+      </x:c>
+      <x:c r="L16" s="302">
+        <x:v>3.688275776795085e-07</x:v>
+      </x:c>
+      <x:c r="M16" s="302">
+        <x:v>0.00010344482636843086</x:v>
       </x:c>
       <x:c r="N16" s="301" t="str">
         <x:v>DERIVED BY SYMMETRY</x:v>
       </x:c>
       <x:c r="O16" s="301" t="str">
-        <x:v>CAD symmetry-derived from LF: local Y reflection</x:v>
+        <x:v>CAD symmetry-derived from LF: Y reflection of LF</x:v>
       </x:c>
       <x:c r="P16" s="301" t="str">
-        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_lower_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="Q16" s="301" t="str">
-        <x:v>URDF &lt;inertial&gt; ready</x:v>
+        <x:v>URDF &lt;inertial&gt; updated 2026-10-31</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -8692,47 +10709,47 @@
       <x:c r="C17" s="301" t="str">
         <x:v>Foot subassembly</x:v>
       </x:c>
-      <x:c r="D17" s="303" t="n">
-        <x:v>0.0175</x:v>
-      </x:c>
-      <x:c r="E17" s="303" t="n">
-        <x:v>-0.00052</x:v>
-      </x:c>
-      <x:c r="F17" s="303" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="303" t="n">
-        <x:v>0.01548</x:v>
-      </x:c>
-      <x:c r="H17" s="302" t="n">
-        <x:v>0.00000114526961866</x:v>
-      </x:c>
-      <x:c r="I17" s="302" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J17" s="302" t="n">
-        <x:v>-1.55064671079e-8</x:v>
-      </x:c>
-      <x:c r="K17" s="302" t="n">
-        <x:v>0.00000120267175</x:v>
-      </x:c>
-      <x:c r="L17" s="302" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M17" s="302" t="n">
-        <x:v>0.00000114835213134</x:v>
+      <x:c r="D17" s="303">
+        <x:v>0.014</x:v>
+      </x:c>
+      <x:c r="E17" s="303">
+        <x:v>-0.00074</x:v>
+      </x:c>
+      <x:c r="F17" s="303">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="303">
+        <x:v>0.01572</x:v>
+      </x:c>
+      <x:c r="H17" s="302">
+        <x:v>8.920990589937979e-07</x:v>
+      </x:c>
+      <x:c r="I17" s="302">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="302">
+        <x:v>-5.562092867964478e-09</x:v>
+      </x:c>
+      <x:c r="K17" s="302">
+        <x:v>8.430463999999999e-07</x:v>
+      </x:c>
+      <x:c r="L17" s="302">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="302">
+        <x:v>8.932047410062023e-07</x:v>
       </x:c>
       <x:c r="N17" s="301" t="str">
         <x:v>DERIVED BY SYMMETRY</x:v>
       </x:c>
       <x:c r="O17" s="301" t="str">
-        <x:v>CAD symmetry-derived from LF: identical foot geometry</x:v>
+        <x:v>CAD symmetry-derived from LF: identical foot geometry (LF copied)</x:v>
       </x:c>
       <x:c r="P17" s="301" t="str">
-        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_foot_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="Q17" s="301" t="str">
-        <x:v>URDF &lt;inertial&gt; ready</x:v>
+        <x:v>URDF &lt;inertial&gt; updated 2026-10-31</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -8745,47 +10762,47 @@
       <x:c r="C18" s="301" t="str">
         <x:v>Hip subassembly</x:v>
       </x:c>
-      <x:c r="D18" s="303" t="n">
+      <x:c r="D18" s="303">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="E18" s="303" t="n">
+      <x:c r="E18" s="303">
         <x:v>0.00366</x:v>
       </x:c>
-      <x:c r="F18" s="303" t="n">
+      <x:c r="F18" s="303">
         <x:v>0.02982</x:v>
       </x:c>
-      <x:c r="G18" s="303" t="n">
+      <x:c r="G18" s="303">
         <x:v>0.00694</x:v>
       </x:c>
-      <x:c r="H18" s="302" t="n">
-        <x:v>0.0000402252347591</x:v>
-      </x:c>
-      <x:c r="I18" s="302" t="n">
-        <x:v>-0.00000131462768927</x:v>
-      </x:c>
-      <x:c r="J18" s="302" t="n">
-        <x:v>-0.00000113953716339</x:v>
-      </x:c>
-      <x:c r="K18" s="302" t="n">
-        <x:v>0.000018958128496</x:v>
-      </x:c>
-      <x:c r="L18" s="302" t="n">
-        <x:v>-0.00000446400670021</x:v>
-      </x:c>
-      <x:c r="M18" s="302" t="n">
-        <x:v>0.0000454280867449</x:v>
+      <x:c r="H18" s="302">
+        <x:v>4.022523475913449e-05</x:v>
+      </x:c>
+      <x:c r="I18" s="302">
+        <x:v>-1.3146276892716857e-06</x:v>
+      </x:c>
+      <x:c r="J18" s="302">
+        <x:v>-1.1395371633858386e-06</x:v>
+      </x:c>
+      <x:c r="K18" s="302">
+        <x:v>1.8958128496012147e-05</x:v>
+      </x:c>
+      <x:c r="L18" s="302">
+        <x:v>-4.464006700211402e-06</x:v>
+      </x:c>
+      <x:c r="M18" s="302">
+        <x:v>4.542808674485334e-05</x:v>
       </x:c>
       <x:c r="N18" s="301" t="str">
         <x:v>DERIVED BY SYMMETRY</x:v>
       </x:c>
       <x:c r="O18" s="301" t="str">
-        <x:v>CAD symmetry-derived from LF: same left-side local geometry</x:v>
+        <x:v>CAD symmetry-derived from LF: same left-side frame as LF (rear hip mesh differs from LF by 0.21 mm CoM / 0.8 % inertia: mesh estimate, not CAD)</x:v>
       </x:c>
       <x:c r="P18" s="301" t="str">
-        <x:v>physprop__lf_hip_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_hip_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="Q18" s="301" t="str">
-        <x:v>URDF &lt;inertial&gt; ready</x:v>
+        <x:v>URDF &lt;inertial&gt; updated 2026-10-31</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -8798,47 +10815,47 @@
       <x:c r="C19" s="301" t="str">
         <x:v>Upper-leg subassembly</x:v>
       </x:c>
-      <x:c r="D19" s="303" t="n">
-        <x:v>0.1725</x:v>
-      </x:c>
-      <x:c r="E19" s="303" t="n">
-        <x:v>0.00108</x:v>
-      </x:c>
-      <x:c r="F19" s="303" t="n">
-        <x:v>0.00015</x:v>
-      </x:c>
-      <x:c r="G19" s="303" t="n">
+      <x:c r="D19" s="303">
+        <x:v>0.152</x:v>
+      </x:c>
+      <x:c r="E19" s="303">
+        <x:v>0.00122</x:v>
+      </x:c>
+      <x:c r="F19" s="303">
+        <x:v>0.00014</x:v>
+      </x:c>
+      <x:c r="G19" s="303">
         <x:v>-0.04503</x:v>
       </x:c>
-      <x:c r="H19" s="302" t="n">
-        <x:v>0.000205436660094</x:v>
-      </x:c>
-      <x:c r="I19" s="302" t="n">
-        <x:v>-5.63507198417e-8</x:v>
-      </x:c>
-      <x:c r="J19" s="302" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K19" s="302" t="n">
-        <x:v>0.000199175976156</x:v>
-      </x:c>
-      <x:c r="L19" s="302" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M19" s="302" t="n">
-        <x:v>0.00003111294525</x:v>
+      <x:c r="H19" s="302">
+        <x:v>0.0001793475307052647</x:v>
+      </x:c>
+      <x:c r="I19" s="302">
+        <x:v>-6.26631577579123e-08</x:v>
+      </x:c>
+      <x:c r="J19" s="302">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K19" s="302">
+        <x:v>0.0001736515692947353</x:v>
+      </x:c>
+      <x:c r="L19" s="302">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M19" s="302">
+        <x:v>2.8445644799999997e-05</x:v>
       </x:c>
       <x:c r="N19" s="301" t="str">
         <x:v>DERIVED BY SYMMETRY</x:v>
       </x:c>
       <x:c r="O19" s="301" t="str">
-        <x:v>CAD symmetry-derived from LF: same left-side local geometry</x:v>
+        <x:v>CAD symmetry-derived from LF: same left-side frame as LF</x:v>
       </x:c>
       <x:c r="P19" s="301" t="str">
-        <x:v>physprop__lf_upper_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_upper_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="Q19" s="301" t="str">
-        <x:v>URDF &lt;inertial&gt; ready</x:v>
+        <x:v>URDF &lt;inertial&gt; updated 2026-10-31</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -8851,47 +10868,47 @@
       <x:c r="C20" s="301" t="str">
         <x:v>Lower-leg subassembly</x:v>
       </x:c>
-      <x:c r="D20" s="303" t="n">
-        <x:v>0.0595</x:v>
-      </x:c>
-      <x:c r="E20" s="303" t="n">
+      <x:c r="D20" s="303">
+        <x:v>0.059</x:v>
+      </x:c>
+      <x:c r="E20" s="303">
         <x:v>0.03075</x:v>
       </x:c>
-      <x:c r="F20" s="303" t="n">
+      <x:c r="F20" s="303">
         <x:v>-0.00118</x:v>
       </x:c>
-      <x:c r="G20" s="303" t="n">
+      <x:c r="G20" s="303">
         <x:v>-0.01958</x:v>
       </x:c>
-      <x:c r="H20" s="302" t="n">
-        <x:v>0.0000215172642767</x:v>
-      </x:c>
-      <x:c r="I20" s="302" t="n">
-        <x:v>6.0930015348e-7</x:v>
-      </x:c>
-      <x:c r="J20" s="302" t="n">
-        <x:v>0.0000168302311374</x:v>
-      </x:c>
-      <x:c r="K20" s="302" t="n">
-        <x:v>0.000102530052784</x:v>
-      </x:c>
-      <x:c r="L20" s="302" t="n">
-        <x:v>-3.71953235117e-7</x:v>
-      </x:c>
-      <x:c r="M20" s="302" t="n">
-        <x:v>0.000104321477439</x:v>
+      <x:c r="H20" s="302">
+        <x:v>2.1336446929790997e-05</x:v>
+      </x:c>
+      <x:c r="I20" s="302">
+        <x:v>6.041799841230725e-07</x:v>
+      </x:c>
+      <x:c r="J20" s="302">
+        <x:v>1.6688800623674613e-05</x:v>
+      </x:c>
+      <x:c r="K20" s="302">
+        <x:v>0.00010166845570177805</x:v>
+      </x:c>
+      <x:c r="L20" s="302">
+        <x:v>-3.688275776795085e-07</x:v>
+      </x:c>
+      <x:c r="M20" s="302">
+        <x:v>0.00010344482636843086</x:v>
       </x:c>
       <x:c r="N20" s="301" t="str">
         <x:v>DERIVED BY SYMMETRY</x:v>
       </x:c>
       <x:c r="O20" s="301" t="str">
-        <x:v>CAD symmetry-derived from LF: same left-side local geometry</x:v>
+        <x:v>CAD symmetry-derived from LF: same left-side frame as LF</x:v>
       </x:c>
       <x:c r="P20" s="301" t="str">
-        <x:v>physprop__lf_lower_leg_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_lower_leg_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="Q20" s="301" t="str">
-        <x:v>URDF &lt;inertial&gt; ready</x:v>
+        <x:v>URDF &lt;inertial&gt; updated 2026-10-31</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -8904,47 +10921,79 @@
       <x:c r="C21" s="301" t="str">
         <x:v>Foot subassembly</x:v>
       </x:c>
-      <x:c r="D21" s="303" t="n">
-        <x:v>0.0175</x:v>
-      </x:c>
-      <x:c r="E21" s="303" t="n">
-        <x:v>-0.00052</x:v>
-      </x:c>
-      <x:c r="F21" s="303" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="303" t="n">
-        <x:v>0.01548</x:v>
-      </x:c>
-      <x:c r="H21" s="302" t="n">
-        <x:v>0.00000114526961866</x:v>
-      </x:c>
-      <x:c r="I21" s="302" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J21" s="302" t="n">
-        <x:v>-1.55064671079e-8</x:v>
-      </x:c>
-      <x:c r="K21" s="302" t="n">
-        <x:v>0.00000120267175</x:v>
-      </x:c>
-      <x:c r="L21" s="302" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M21" s="302" t="n">
-        <x:v>0.00000114835213134</x:v>
+      <x:c r="D21" s="303">
+        <x:v>0.014</x:v>
+      </x:c>
+      <x:c r="E21" s="303">
+        <x:v>-0.00074</x:v>
+      </x:c>
+      <x:c r="F21" s="303">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G21" s="303">
+        <x:v>0.01572</x:v>
+      </x:c>
+      <x:c r="H21" s="302">
+        <x:v>8.920990589937979e-07</x:v>
+      </x:c>
+      <x:c r="I21" s="302">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J21" s="302">
+        <x:v>-5.562092867964478e-09</x:v>
+      </x:c>
+      <x:c r="K21" s="302">
+        <x:v>8.430463999999999e-07</x:v>
+      </x:c>
+      <x:c r="L21" s="302">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M21" s="302">
+        <x:v>8.932047410062023e-07</x:v>
       </x:c>
       <x:c r="N21" s="301" t="str">
         <x:v>DERIVED BY SYMMETRY</x:v>
       </x:c>
       <x:c r="O21" s="301" t="str">
-        <x:v>CAD symmetry-derived from LF: identical foot geometry</x:v>
+        <x:v>CAD symmetry-derived from LF: identical foot geometry (LF copied)</x:v>
       </x:c>
       <x:c r="P21" s="301" t="str">
-        <x:v>physprop__lf_foot_link.txt + weight_breakdown_summary.txt</x:v>
+        <x:v>lf_foot_link__physprop.txt (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="Q21" s="301" t="str">
-        <x:v>URDF &lt;inertial&gt; ready</x:v>
+        <x:v>URDF &lt;inertial&gt; updated 2026-10-31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str" s="301">
+        <x:v>Nominal model total (17 links) [kg]</x:v>
+      </x:c>
+      <x:c r="D23" s="303">
+        <x:f>SUM(D5:D21)</x:f>
+        <x:v>2.928</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str" s="301">
+        <x:v>Solid Edge assembly report [kg]</x:v>
+      </x:c>
+      <x:c r="D24" s="303">
+        <x:f>CAD_Source_Data!D10</x:f>
+        <x:v>2.937</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str" s="301">
+        <x:v>Difference model − assembly [kg]</x:v>
+      </x:c>
+      <x:c r="D25" s="303">
+        <x:f>D23-D24</x:f>
+        <x:v>-0.008999999999999897</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str" s="301">
+        <x:v>Origin of the difference: per-link masses are reported at 1 g resolution; the 17 link volumes close on the assembly volume within 1.1 mm³, so no solid is missing. Not allocated to any link (see Mass_Reconciliation).</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8982,7 +11031,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="289" t="str">
-        <x:v>MATDOG — Dati CAD sorgente per proprietà fisiche</x:v>
+        <x:v>MATDOG — Dati CAD sorgente per proprietà fisiche (Solid Edge 2026-10-30)</x:v>
       </x:c>
       <x:c r="B1" s="289"/>
       <x:c r="C1" s="289"/>
@@ -9004,7 +11053,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="294" t="str">
-        <x:v>Trascrizione strutturata dei report Solid Edge ricevuti. I valori di massa per URDF usano la tabella CAD riconciliata; i report per-link visualizzano la massa arrotondata a 0.001 kg.</x:v>
+        <x:v>Trascrizione strutturata dei report Solid Edge ricevuti il 2026-10-30 (configurazione nominale con Jetson Orin). I report per-link riportano la massa a 0.001 kg; i momenti 'global' sono riferiti all’origine CAD, non al CoM, e sono in kg·dm² come stampati. Gli originali sono in 09_Logs/Validation_Reports/REV01_FIX_Physical_Properties_2026-10-31/input/.</x:v>
       </x:c>
       <x:c r="B2" s="294"/>
       <x:c r="C2" s="294"/>
@@ -9052,22 +11101,22 @@
 [mm]</x:v>
       </x:c>
       <x:c r="H4" s="305" t="str">
-        <x:v>Ixx global</x:v>
+        <x:v>Ixx global [kg·dm²]</x:v>
       </x:c>
       <x:c r="I4" s="305" t="str">
-        <x:v>Iyy global</x:v>
+        <x:v>Iyy global [kg·dm²]</x:v>
       </x:c>
       <x:c r="J4" s="305" t="str">
-        <x:v>Izz global</x:v>
+        <x:v>Izz global [kg·dm²]</x:v>
       </x:c>
       <x:c r="K4" s="305" t="str">
-        <x:v>Ixy product</x:v>
+        <x:v>Ixy product [kg·dm²]</x:v>
       </x:c>
       <x:c r="L4" s="305" t="str">
-        <x:v>Ixz product</x:v>
+        <x:v>Ixz product [kg·dm²]</x:v>
       </x:c>
       <x:c r="M4" s="305" t="str">
-        <x:v>Iyz product</x:v>
+        <x:v>Iyz product [kg·dm²]</x:v>
       </x:c>
       <x:c r="N4" s="305" t="str">
         <x:v>K1
@@ -9082,7 +11131,7 @@
 [mm]</x:v>
       </x:c>
       <x:c r="Q4" s="305" t="str">
-        <x:v>Use in REV00</x:v>
+        <x:v>Use in REV01-FIX</x:v>
       </x:c>
       <x:c r="R4" s="305" t="str">
         <x:v>Notes</x:v>
@@ -9090,338 +11139,344 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="301" t="str">
-        <x:v>physprop__base_link.txt</x:v>
+        <x:v>base_link__physprop.txt</x:v>
       </x:c>
       <x:c r="B5" s="301" t="str">
         <x:v>base_link</x:v>
       </x:c>
-      <x:c r="C5" s="306" t="n">
-        <x:v>1.281</x:v>
-      </x:c>
-      <x:c r="D5" s="306" t="n">
-        <x:v>1.282</x:v>
-      </x:c>
-      <x:c r="E5" s="307" t="n">
-        <x:v>5.84</x:v>
-      </x:c>
-      <x:c r="F5" s="307" t="n">
-        <x:v>-0.65</x:v>
-      </x:c>
-      <x:c r="G5" s="307" t="n">
-        <x:v>27.73</x:v>
-      </x:c>
-      <x:c r="H5" s="303" t="n">
-        <x:v>0.246</x:v>
-      </x:c>
-      <x:c r="I5" s="303" t="n">
-        <x:v>0.989</x:v>
-      </x:c>
-      <x:c r="J5" s="303" t="n">
-        <x:v>0.954</x:v>
-      </x:c>
-      <x:c r="K5" s="303" t="n">
+      <x:c r="C5" s="306">
+        <x:v>1.828</x:v>
+      </x:c>
+      <x:c r="D5" s="306">
+        <x:f>C5</x:f>
+        <x:v>1.828</x:v>
+      </x:c>
+      <x:c r="E5" s="307">
+        <x:v>-6.93</x:v>
+      </x:c>
+      <x:c r="F5" s="307">
+        <x:v>-0.44</x:v>
+      </x:c>
+      <x:c r="G5" s="307">
+        <x:v>36.57</x:v>
+      </x:c>
+      <x:c r="H5" s="303">
+        <x:v>0.433</x:v>
+      </x:c>
+      <x:c r="I5" s="303">
+        <x:v>1.614</x:v>
+      </x:c>
+      <x:c r="J5" s="303">
+        <x:v>1.414</x:v>
+      </x:c>
+      <x:c r="K5" s="303">
+        <x:v>0.002</x:v>
+      </x:c>
+      <x:c r="L5" s="303">
+        <x:v>-0.021</x:v>
+      </x:c>
+      <x:c r="M5" s="303">
         <x:v>-0.002</x:v>
       </x:c>
-      <x:c r="L5" s="303" t="n">
-        <x:v>0.065</x:v>
-      </x:c>
-      <x:c r="M5" s="303" t="n">
-        <x:v>-0.002</x:v>
-      </x:c>
-      <x:c r="N5" s="307" t="n">
-        <x:v>86.19</x:v>
-      </x:c>
-      <x:c r="O5" s="307" t="n">
-        <x:v>83.18</x:v>
-      </x:c>
-      <x:c r="P5" s="307" t="n">
-        <x:v>33.61</x:v>
+      <x:c r="N5" s="307">
+        <x:v>87.7</x:v>
+      </x:c>
+      <x:c r="O5" s="307">
+        <x:v>86.28</x:v>
+      </x:c>
+      <x:c r="P5" s="307">
+        <x:v>32.07</x:v>
       </x:c>
       <x:c r="Q5" s="301" t="str">
         <x:v>Direct</x:v>
       </x:c>
       <x:c r="R5" s="301" t="str">
-        <x:v>Mass used is the CAD-reconciliation value from weight_breakdown_summary.txt.</x:v>
+        <x:v>Includes the Jetson Orin (175 g). Mass used = Solid Edge report.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="301" t="str">
-        <x:v>physprop__lf_hip_link.txt</x:v>
+        <x:v>lf_hip_link__physprop.txt</x:v>
       </x:c>
       <x:c r="B6" s="301" t="str">
         <x:v>lf_hip_link</x:v>
       </x:c>
-      <x:c r="C6" s="306" t="n">
+      <x:c r="C6" s="306">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="D6" s="306" t="n">
+      <x:c r="D6" s="306">
+        <x:f>C6</x:f>
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="E6" s="307" t="n">
+      <x:c r="E6" s="307">
         <x:v>3.66</x:v>
       </x:c>
-      <x:c r="F6" s="307" t="n">
+      <x:c r="F6" s="307">
         <x:v>29.82</x:v>
       </x:c>
-      <x:c r="G6" s="307" t="n">
+      <x:c r="G6" s="307">
         <x:v>6.94</x:v>
       </x:c>
-      <x:c r="H6" s="303" t="n">
+      <x:c r="H6" s="303">
         <x:v>0.009</x:v>
       </x:c>
-      <x:c r="I6" s="303" t="n">
+      <x:c r="I6" s="303">
         <x:v>0.002</x:v>
       </x:c>
-      <x:c r="J6" s="303" t="n">
+      <x:c r="J6" s="303">
         <x:v>0.009</x:v>
       </x:c>
-      <x:c r="K6" s="303" t="n">
+      <x:c r="K6" s="303">
         <x:v>0.001</x:v>
       </x:c>
-      <x:c r="L6" s="303" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M6" s="303" t="n">
+      <x:c r="L6" s="303">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M6" s="303">
         <x:v>0.001</x:v>
       </x:c>
-      <x:c r="N6" s="307" t="n">
+      <x:c r="N6" s="307">
         <x:v>30.43</x:v>
       </x:c>
-      <x:c r="O6" s="307" t="n">
+      <x:c r="O6" s="307">
         <x:v>28.35</x:v>
       </x:c>
-      <x:c r="P6" s="307" t="n">
+      <x:c r="P6" s="307">
         <x:v>19.04</x:v>
       </x:c>
       <x:c r="Q6" s="301" t="str">
         <x:v>Direct LF / symmetry seed</x:v>
       </x:c>
       <x:c r="R6" s="301" t="str">
-        <x:v>RF and RH are derived by local Y reflection; LH uses the same left-side local geometry.</x:v>
+        <x:v>RF = Y reflection of LF; LH = LF frame; RH = Y reflection (rear hip meshes differ slightly from LF: see Physical_Property_Method).</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="301" t="str">
-        <x:v>physprop__lf_upper_leg_link.txt</x:v>
+        <x:v>lf_upper_leg_link__physprop.txt</x:v>
       </x:c>
       <x:c r="B7" s="301" t="str">
         <x:v>lf_upper_leg_link</x:v>
       </x:c>
-      <x:c r="C7" s="306" t="n">
-        <x:v>0.172</x:v>
-      </x:c>
-      <x:c r="D7" s="306" t="n">
-        <x:v>0.1725</x:v>
-      </x:c>
-      <x:c r="E7" s="307" t="n">
-        <x:v>1.08</x:v>
-      </x:c>
-      <x:c r="F7" s="307" t="n">
-        <x:v>0.15</x:v>
-      </x:c>
-      <x:c r="G7" s="307" t="n">
+      <x:c r="C7" s="306">
+        <x:v>0.152</x:v>
+      </x:c>
+      <x:c r="D7" s="306">
+        <x:f>C7</x:f>
+        <x:v>0.152</x:v>
+      </x:c>
+      <x:c r="E7" s="307">
+        <x:v>1.22</x:v>
+      </x:c>
+      <x:c r="F7" s="307">
+        <x:v>0.14</x:v>
+      </x:c>
+      <x:c r="G7" s="307">
         <x:v>-45.03</x:v>
       </x:c>
-      <x:c r="H7" s="303" t="n">
-        <x:v>0.055</x:v>
-      </x:c>
-      <x:c r="I7" s="303" t="n">
-        <x:v>0.055</x:v>
-      </x:c>
-      <x:c r="J7" s="303" t="n">
+      <x:c r="H7" s="303">
+        <x:v>0.049</x:v>
+      </x:c>
+      <x:c r="I7" s="303">
+        <x:v>0.048</x:v>
+      </x:c>
+      <x:c r="J7" s="303">
         <x:v>0.003</x:v>
       </x:c>
-      <x:c r="K7" s="303" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L7" s="303" t="n">
+      <x:c r="K7" s="303">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L7" s="303">
         <x:v>-0.001</x:v>
       </x:c>
-      <x:c r="M7" s="303" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="307" t="n">
-        <x:v>34.51</x:v>
-      </x:c>
-      <x:c r="O7" s="307" t="n">
-        <x:v>33.98</x:v>
-      </x:c>
-      <x:c r="P7" s="307" t="n">
-        <x:v>13.43</x:v>
+      <x:c r="M7" s="303">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N7" s="307">
+        <x:v>34.35</x:v>
+      </x:c>
+      <x:c r="O7" s="307">
+        <x:v>33.8</x:v>
+      </x:c>
+      <x:c r="P7" s="307">
+        <x:v>13.68</x:v>
       </x:c>
       <x:c r="Q7" s="301" t="str">
         <x:v>Direct LF / symmetry seed</x:v>
       </x:c>
       <x:c r="R7" s="301" t="str">
-        <x:v>RF and RH are derived by local Y reflection; LH uses the same left-side local geometry.</x:v>
+        <x:v>RF and RH are derived by local Y reflection; LH uses the same left-side local geometry (mesh-verified).</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="301" t="str">
-        <x:v>physprop__lf_lower_leg_link.txt</x:v>
+        <x:v>lf_lower_leg_link__physprop.txt</x:v>
       </x:c>
       <x:c r="B8" s="301" t="str">
         <x:v>lf_lower_leg_link</x:v>
       </x:c>
-      <x:c r="C8" s="306" t="n">
+      <x:c r="C8" s="306">
         <x:v>0.059</x:v>
       </x:c>
-      <x:c r="D8" s="306" t="n">
-        <x:v>0.0595</x:v>
-      </x:c>
-      <x:c r="E8" s="307" t="n">
+      <x:c r="D8" s="306">
+        <x:f>C8</x:f>
+        <x:v>0.059</x:v>
+      </x:c>
+      <x:c r="E8" s="307">
         <x:v>30.75</x:v>
       </x:c>
-      <x:c r="F8" s="307" t="n">
+      <x:c r="F8" s="307">
         <x:v>-1.18</x:v>
       </x:c>
-      <x:c r="G8" s="307" t="n">
+      <x:c r="G8" s="307">
         <x:v>-19.58</x:v>
       </x:c>
-      <x:c r="H8" s="303" t="n">
+      <x:c r="H8" s="303">
         <x:v>0.004</x:v>
       </x:c>
-      <x:c r="I8" s="303" t="n">
+      <x:c r="I8" s="303">
         <x:v>0.018</x:v>
       </x:c>
-      <x:c r="J8" s="303" t="n">
+      <x:c r="J8" s="303">
         <x:v>0.016</x:v>
       </x:c>
-      <x:c r="K8" s="303" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L8" s="303" t="n">
+      <x:c r="K8" s="303">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L8" s="303">
         <x:v>-0.005</x:v>
       </x:c>
-      <x:c r="M8" s="303" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="307" t="n">
+      <x:c r="M8" s="303">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N8" s="307">
         <x:v>42.53</x:v>
       </x:c>
-      <x:c r="O8" s="307" t="n">
+      <x:c r="O8" s="307">
         <x:v>41.51</x:v>
       </x:c>
-      <x:c r="P8" s="307" t="n">
+      <x:c r="P8" s="307">
         <x:v>17.5</x:v>
       </x:c>
       <x:c r="Q8" s="301" t="str">
         <x:v>Direct LF / symmetry seed</x:v>
       </x:c>
       <x:c r="R8" s="301" t="str">
-        <x:v>RF and RH are derived by local Y reflection; LH uses the same left-side local geometry.</x:v>
+        <x:v>RF and RH are derived by local Y reflection; LH uses the same left-side local geometry (mesh-verified).</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="301" t="str">
-        <x:v>physprop__lf_foot_link.txt</x:v>
+        <x:v>lf_foot_link__physprop.txt</x:v>
       </x:c>
       <x:c r="B9" s="301" t="str">
         <x:v>lf_foot_link</x:v>
       </x:c>
-      <x:c r="C9" s="306" t="n">
-        <x:v>0.017</x:v>
-      </x:c>
-      <x:c r="D9" s="306" t="n">
-        <x:v>0.0175</x:v>
-      </x:c>
-      <x:c r="E9" s="307" t="n">
-        <x:v>-0.52</x:v>
-      </x:c>
-      <x:c r="F9" s="307" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="307" t="n">
-        <x:v>15.48</x:v>
-      </x:c>
-      <x:c r="H9" s="303" t="n">
-        <x:v>0.001</x:v>
-      </x:c>
-      <x:c r="I9" s="303" t="n">
-        <x:v>0.001</x:v>
-      </x:c>
-      <x:c r="J9" s="303" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K9" s="303" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L9" s="303" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M9" s="303" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="307" t="n">
-        <x:v>8.29</x:v>
-      </x:c>
-      <x:c r="O9" s="307" t="n">
-        <x:v>8.15</x:v>
-      </x:c>
-      <x:c r="P9" s="307" t="n">
-        <x:v>8.04</x:v>
+      <x:c r="C9" s="306">
+        <x:v>0.014</x:v>
+      </x:c>
+      <x:c r="D9" s="306">
+        <x:f>C9</x:f>
+        <x:v>0.014</x:v>
+      </x:c>
+      <x:c r="E9" s="307">
+        <x:v>-0.74</x:v>
+      </x:c>
+      <x:c r="F9" s="307">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="307">
+        <x:v>15.72</x:v>
+      </x:c>
+      <x:c r="H9" s="303">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I9" s="303">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="303">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K9" s="303">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L9" s="303">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" s="303">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N9" s="307">
+        <x:v>8.01</x:v>
+      </x:c>
+      <x:c r="O9" s="307">
+        <x:v>7.96</x:v>
+      </x:c>
+      <x:c r="P9" s="307">
+        <x:v>7.76</x:v>
       </x:c>
       <x:c r="Q9" s="301" t="str">
         <x:v>Direct LF / identical foot seed</x:v>
       </x:c>
       <x:c r="R9" s="301" t="str">
-        <x:v>All four foot links use the identical CAD foot geometry.</x:v>
+        <x:v>All four foot links use the identical CAD foot geometry. Global moments print as 0.000 because of rounding (&lt; 5e-6 kg·m²), not because the inertia is zero.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="301" t="str">
-        <x:v>physprop__robotdog_assembly.txt</x:v>
+        <x:v>matdog_urdf_assembly__physprop.txt</x:v>
       </x:c>
       <x:c r="B10" s="301" t="str">
-        <x:v>17-link assembly</x:v>
-      </x:c>
-      <x:c r="C10" s="306" t="n">
-        <x:v>2.48</x:v>
-      </x:c>
-      <x:c r="D10" s="306" t="n">
-        <x:v>2.48</x:v>
-      </x:c>
-      <x:c r="E10" s="307" t="n">
-        <x:v>9.48</x:v>
-      </x:c>
-      <x:c r="F10" s="307" t="n">
-        <x:v>-0.71</x:v>
-      </x:c>
-      <x:c r="G10" s="307" t="n">
-        <x:v>5.91</x:v>
-      </x:c>
-      <x:c r="H10" s="303" t="n">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="I10" s="303" t="n">
-        <x:v>0.03</x:v>
-      </x:c>
-      <x:c r="J10" s="303" t="n">
-        <x:v>0.037</x:v>
-      </x:c>
-      <x:c r="K10" s="303" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L10" s="303" t="n">
-        <x:v>0.001</x:v>
-      </x:c>
-      <x:c r="M10" s="303" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="307" t="n">
-        <x:v>121.31</x:v>
-      </x:c>
-      <x:c r="O10" s="307" t="n">
-        <x:v>108.92</x:v>
-      </x:c>
-      <x:c r="P10" s="307" t="n">
-        <x:v>80.42</x:v>
+        <x:v>17-link assembly (frame Base; moments about the CoM, kg·m² printed, converted to kg·dm² here)</x:v>
+      </x:c>
+      <x:c r="C10" s="306">
+        <x:v>2.937</x:v>
+      </x:c>
+      <x:c r="D10" s="306">
+        <x:f>C10</x:f>
+        <x:v>2.937</x:v>
+      </x:c>
+      <x:c r="E10" s="307">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="F10" s="307">
+        <x:v>-0.59</x:v>
+      </x:c>
+      <x:c r="G10" s="307">
+        <x:v>17.02</x:v>
+      </x:c>
+      <x:c r="H10" s="303">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="I10" s="303">
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="J10" s="303">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="K10" s="303">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L10" s="303">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M10" s="303">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N10" s="307">
+        <x:v>115.56</x:v>
+      </x:c>
+      <x:c r="O10" s="307">
+        <x:v>106.96</x:v>
+      </x:c>
+      <x:c r="P10" s="307">
+        <x:v>73.98</x:v>
       </x:c>
       <x:c r="Q10" s="301" t="str">
         <x:v>Aggregate validation</x:v>
       </x:c>
       <x:c r="R10" s="301" t="str">
-        <x:v>User notes that the neck yaw actuator is not represented by this assembly scope; no standalone neck link is added to REV00.</x:v>
+        <x:v>Includes the Jetson Orin. Rebuilt 17-link model: 2.928 kg, CoM deviation 0.42 mm, K within 0.2 %. Volume: assembly 1970535.851 mm³ vs sum of link volumes 1970534.788 mm³.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/03_CAD/URDF/matt_robodog_rev00/reference/Coordinate_Cinematiche_matt_robodog_rev00.xlsx
+++ b/03_CAD/URDF/matt_robodog_rev00/reference/Coordinate_Cinematiche_matt_robodog_rev00.xlsx
@@ -8335,10 +8335,6 @@
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A2:F2"/>
-    <x:mergeCell ref="A13:F13"/>
-    <x:mergeCell ref="A13:F14"/>
-    <x:mergeCell ref="A1:B1"/>
-    <x:mergeCell ref="A2:B2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/03_CAD/URDF/matt_robodog_rev00/reference/Coordinate_Cinematiche_matt_robodog_rev00.xlsx
+++ b/03_CAD/URDF/matt_robodog_rev00/reference/Coordinate_Cinematiche_matt_robodog_rev00.xlsx
@@ -1722,10 +1722,10 @@
     <x:tableColumn id="18" name="Z parent&#10;[m]"/>
     <x:tableColumn id="19" name="θ min&#10;[rad]"/>
     <x:tableColumn id="20" name="θ max&#10;[rad]"/>
-    <x:tableColumn id="21" name="Speed&#10;[rpm]"/>
+    <x:tableColumn id="21" name="Tetto a vuoto 3S&#10;[ RPM ]"/>
     <x:tableColumn id="22" name="Speed&#10;[rad/s]"/>
-    <x:tableColumn id="23" name="Torque&#10;[kg·cm]"/>
-    <x:tableColumn id="24" name="Effort&#10;[N·m]"/>
+    <x:tableColumn id="23" name="Budget coppia 3S&#10;[kg·cm]"/>
+    <x:tableColumn id="24" name="Budget coppia 3S&#10;[N·m]"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </x:table>
